--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129649680</v>
       </c>
       <c r="B2" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649665</v>
+        <v>129649690</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438999</v>
+        <v>438937</v>
       </c>
       <c r="R3" t="n">
-        <v>6811646</v>
+        <v>6811799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>129649751</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649730</v>
+        <v>129649665</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439044</v>
+        <v>438999</v>
       </c>
       <c r="R5" t="n">
-        <v>6811698</v>
+        <v>6811646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B6" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649729</v>
+        <v>129649734</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439018</v>
+        <v>439124</v>
       </c>
       <c r="R8" t="n">
-        <v>6811719</v>
+        <v>6811683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649734</v>
+        <v>129649729</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439124</v>
+        <v>439018</v>
       </c>
       <c r="R9" t="n">
-        <v>6811683</v>
+        <v>6811719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>129649749</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649693</v>
+        <v>129649700</v>
       </c>
       <c r="B11" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439138</v>
+        <v>438940</v>
       </c>
       <c r="R11" t="n">
-        <v>6811630</v>
+        <v>6811804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
         <v>129649699</v>
       </c>
       <c r="B12" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,45 +1750,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649700</v>
+        <v>129649684</v>
       </c>
       <c r="B13" t="n">
-        <v>78827</v>
+        <v>56928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438940</v>
+        <v>439120</v>
       </c>
       <c r="R13" t="n">
-        <v>6811804</v>
+        <v>6811610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,53 +1855,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649684</v>
+        <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>56923</v>
+        <v>78833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439120</v>
+        <v>439138</v>
       </c>
       <c r="R14" t="n">
-        <v>6811610</v>
+        <v>6811630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129649683</v>
+        <v>129649682</v>
       </c>
       <c r="B16" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439106</v>
+        <v>439062</v>
       </c>
       <c r="R16" t="n">
         <v>6811611</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649682</v>
+        <v>129649683</v>
       </c>
       <c r="B17" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439062</v>
+        <v>439106</v>
       </c>
       <c r="R17" t="n">
         <v>6811611</v>
@@ -2262,7 +2262,7 @@
         <v>129649667</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649704</v>
+        <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439142</v>
+        <v>439071</v>
       </c>
       <c r="R19" t="n">
-        <v>6811627</v>
+        <v>6811718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649701</v>
+        <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439071</v>
+        <v>439142</v>
       </c>
       <c r="R20" t="n">
-        <v>6811718</v>
+        <v>6811627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,7 +2553,7 @@
         <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>129649681</v>
       </c>
       <c r="B22" t="n">
-        <v>56923</v>
+        <v>56928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,45 +3048,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649663</v>
+        <v>129649679</v>
       </c>
       <c r="B26" t="n">
-        <v>79689</v>
+        <v>56928</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439158</v>
+        <v>439074</v>
       </c>
       <c r="R26" t="n">
-        <v>6811692</v>
+        <v>6811666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,53 +3153,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649679</v>
+        <v>129649746</v>
       </c>
       <c r="B27" t="n">
-        <v>56923</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439074</v>
+        <v>439029</v>
       </c>
       <c r="R27" t="n">
-        <v>6811666</v>
+        <v>6811655</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>129649756</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649746</v>
+        <v>129649663</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439029</v>
+        <v>439158</v>
       </c>
       <c r="R29" t="n">
-        <v>6811655</v>
+        <v>6811692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649731</v>
+        <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439095</v>
+        <v>438992</v>
       </c>
       <c r="R30" t="n">
-        <v>6811729</v>
+        <v>6811688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129649743</v>
+        <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438992</v>
+        <v>439095</v>
       </c>
       <c r="R31" t="n">
-        <v>6811688</v>
+        <v>6811729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R32" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R33" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649688</v>
+        <v>129649705</v>
       </c>
       <c r="B34" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438959</v>
+        <v>439072</v>
       </c>
       <c r="R34" t="n">
-        <v>6811760</v>
+        <v>6811591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649705</v>
+        <v>129649740</v>
       </c>
       <c r="B35" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439072</v>
+        <v>439121</v>
       </c>
       <c r="R35" t="n">
-        <v>6811591</v>
+        <v>6811628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B36" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R36" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649740</v>
+        <v>129649666</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439121</v>
+        <v>439131</v>
       </c>
       <c r="R37" t="n">
-        <v>6811628</v>
+        <v>6811582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4223,7 +4223,7 @@
         <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>129649752</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>129649742</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649702</v>
+        <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>78827</v>
+        <v>91608</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439157</v>
+        <v>439053</v>
       </c>
       <c r="R42" t="n">
-        <v>6811682</v>
+        <v>6811673</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4679,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4710,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649733</v>
+        <v>129649747</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439097</v>
+        <v>439069</v>
       </c>
       <c r="R43" t="n">
-        <v>6811705</v>
+        <v>6811626</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649738</v>
+        <v>129649733</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4837,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439156</v>
+        <v>439097</v>
       </c>
       <c r="R44" t="n">
-        <v>6811648</v>
+        <v>6811705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649747</v>
+        <v>129649738</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439069</v>
+        <v>439156</v>
       </c>
       <c r="R45" t="n">
-        <v>6811626</v>
+        <v>6811648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4996,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649736</v>
+        <v>129649702</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +5012,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439165</v>
+        <v>439157</v>
       </c>
       <c r="R46" t="n">
-        <v>6811686</v>
+        <v>6811682</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5093,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649677</v>
+        <v>129649736</v>
       </c>
       <c r="B47" t="n">
-        <v>91602</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,21 +5109,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439053</v>
+        <v>439165</v>
       </c>
       <c r="R47" t="n">
-        <v>6811673</v>
+        <v>6811686</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5164,11 +5169,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5198,7 +5198,7 @@
         <v>129649725</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5486,53 +5486,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649685</v>
+        <v>129649697</v>
       </c>
       <c r="B51" t="n">
-        <v>56923</v>
+        <v>78832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439104</v>
+        <v>438961</v>
       </c>
       <c r="R51" t="n">
-        <v>6811591</v>
+        <v>6811763</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5591,10 +5583,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649697</v>
+        <v>129649728</v>
       </c>
       <c r="B52" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5602,21 +5594,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5626,10 +5618,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438961</v>
+        <v>438994</v>
       </c>
       <c r="R52" t="n">
-        <v>6811763</v>
+        <v>6811747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5688,45 +5680,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649728</v>
+        <v>129649685</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>56928</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438994</v>
+        <v>439104</v>
       </c>
       <c r="R53" t="n">
-        <v>6811747</v>
+        <v>6811591</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649737</v>
+        <v>129649732</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439170</v>
+        <v>439106</v>
       </c>
       <c r="R55" t="n">
-        <v>6811661</v>
+        <v>6811690</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649732</v>
+        <v>129649737</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439106</v>
+        <v>439170</v>
       </c>
       <c r="R56" t="n">
-        <v>6811690</v>
+        <v>6811661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6079,7 +6079,7 @@
         <v>129649703</v>
       </c>
       <c r="B57" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649754</v>
+        <v>129649676</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,34 +6383,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439022</v>
+        <v>438971</v>
       </c>
       <c r="R60" t="n">
-        <v>6811624</v>
+        <v>6811657</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6443,6 +6451,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6469,10 +6482,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649739</v>
+        <v>129649664</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6480,21 +6493,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6504,10 +6517,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439148</v>
+        <v>439138</v>
       </c>
       <c r="R61" t="n">
-        <v>6811637</v>
+        <v>6811625</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6579,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649691</v>
+        <v>129649754</v>
       </c>
       <c r="B62" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6590,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6614,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439156</v>
+        <v>439022</v>
       </c>
       <c r="R62" t="n">
-        <v>6811687</v>
+        <v>6811624</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6663,10 +6676,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649664</v>
+        <v>129649739</v>
       </c>
       <c r="B63" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,21 +6687,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6698,10 +6711,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439138</v>
+        <v>439148</v>
       </c>
       <c r="R63" t="n">
-        <v>6811625</v>
+        <v>6811637</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6760,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649676</v>
+        <v>129649691</v>
       </c>
       <c r="B64" t="n">
-        <v>57890</v>
+        <v>78833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6771,42 +6784,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438971</v>
+        <v>439156</v>
       </c>
       <c r="R64" t="n">
-        <v>6811657</v>
+        <v>6811687</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6839,11 +6844,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649750</v>
+        <v>129649696</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R65" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649672</v>
+        <v>129649750</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438973</v>
+        <v>439104</v>
       </c>
       <c r="R66" t="n">
-        <v>6811633</v>
+        <v>6811588</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649687</v>
+        <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>78828</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R67" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649696</v>
+        <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>78827</v>
+        <v>78833</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7261,7 +7261,7 @@
         <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>129660885</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660855</v>
+        <v>129660835</v>
       </c>
       <c r="B79" t="n">
-        <v>78827</v>
+        <v>79665</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438795</v>
+        <v>438807</v>
       </c>
       <c r="R79" t="n">
-        <v>6811815</v>
+        <v>6811845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,32 +8325,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B80" t="n">
-        <v>56920</v>
+        <v>57735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R80" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660839</v>
+        <v>129660855</v>
       </c>
       <c r="B81" t="n">
-        <v>57730</v>
+        <v>78832</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8441,42 +8441,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438773</v>
+        <v>438795</v>
       </c>
       <c r="R81" t="n">
-        <v>6811783</v>
+        <v>6811815</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8535,45 +8527,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660835</v>
+        <v>129660841</v>
       </c>
       <c r="B82" t="n">
-        <v>79660</v>
+        <v>56925</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438807</v>
+        <v>438785</v>
       </c>
       <c r="R82" t="n">
-        <v>6811845</v>
+        <v>6811874</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
         <v>129660842</v>
       </c>
       <c r="B83" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,34 +8748,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R84" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8834,10 +8842,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8845,42 +8853,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R85" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8942,7 +8942,7 @@
         <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>129660844</v>
       </c>
       <c r="B87" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129649680</v>
       </c>
       <c r="B2" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129649690</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129649751</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649665</v>
+        <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438999</v>
+        <v>439044</v>
       </c>
       <c r="R5" t="n">
-        <v>6811646</v>
+        <v>6811698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649730</v>
+        <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439044</v>
+        <v>438999</v>
       </c>
       <c r="R6" t="n">
-        <v>6811698</v>
+        <v>6811646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649734</v>
+        <v>129649729</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439124</v>
+        <v>439018</v>
       </c>
       <c r="R8" t="n">
-        <v>6811683</v>
+        <v>6811719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649729</v>
+        <v>129649734</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439018</v>
+        <v>439124</v>
       </c>
       <c r="R9" t="n">
-        <v>6811719</v>
+        <v>6811683</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>129649749</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649700</v>
+        <v>129649693</v>
       </c>
       <c r="B11" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438940</v>
+        <v>439138</v>
       </c>
       <c r="R11" t="n">
-        <v>6811804</v>
+        <v>6811630</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649699</v>
+        <v>129649700</v>
       </c>
       <c r="B12" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438935</v>
+        <v>438940</v>
       </c>
       <c r="R12" t="n">
-        <v>6811797</v>
+        <v>6811804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,53 +1750,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649684</v>
+        <v>129649699</v>
       </c>
       <c r="B13" t="n">
-        <v>56928</v>
+        <v>78833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439120</v>
+        <v>438935</v>
       </c>
       <c r="R13" t="n">
-        <v>6811610</v>
+        <v>6811797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,45 +1847,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649693</v>
+        <v>129649684</v>
       </c>
       <c r="B14" t="n">
-        <v>78833</v>
+        <v>56929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439138</v>
+        <v>439120</v>
       </c>
       <c r="R14" t="n">
-        <v>6811630</v>
+        <v>6811610</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129649682</v>
       </c>
       <c r="B16" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129649683</v>
       </c>
       <c r="B17" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129649667</v>
       </c>
       <c r="B18" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>129649681</v>
       </c>
       <c r="B22" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,53 +3048,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649679</v>
+        <v>129649663</v>
       </c>
       <c r="B26" t="n">
-        <v>56928</v>
+        <v>79695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439074</v>
+        <v>439158</v>
       </c>
       <c r="R26" t="n">
-        <v>6811666</v>
+        <v>6811692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,10 +3145,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649746</v>
+        <v>129649756</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3188,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439029</v>
+        <v>438993</v>
       </c>
       <c r="R27" t="n">
-        <v>6811655</v>
+        <v>6811613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649756</v>
+        <v>129649746</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3285,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438993</v>
+        <v>439029</v>
       </c>
       <c r="R28" t="n">
-        <v>6811613</v>
+        <v>6811655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,45 +3339,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649663</v>
+        <v>129649679</v>
       </c>
       <c r="B29" t="n">
-        <v>79694</v>
+        <v>56929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439158</v>
+        <v>439074</v>
       </c>
       <c r="R29" t="n">
-        <v>6811692</v>
+        <v>6811666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649705</v>
+        <v>129649740</v>
       </c>
       <c r="B34" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439072</v>
+        <v>439121</v>
       </c>
       <c r="R34" t="n">
-        <v>6811591</v>
+        <v>6811628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649740</v>
+        <v>129649705</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439121</v>
+        <v>439072</v>
       </c>
       <c r="R35" t="n">
-        <v>6811628</v>
+        <v>6811591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649688</v>
+        <v>129649666</v>
       </c>
       <c r="B36" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438959</v>
+        <v>439131</v>
       </c>
       <c r="R36" t="n">
-        <v>6811760</v>
+        <v>6811582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R37" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R38" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649752</v>
+        <v>129649727</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439063</v>
+        <v>438945</v>
       </c>
       <c r="R39" t="n">
-        <v>6811611</v>
+        <v>6811803</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649742</v>
+        <v>129649752</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439038</v>
+        <v>439063</v>
       </c>
       <c r="R40" t="n">
-        <v>6811696</v>
+        <v>6811611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649742</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>439038</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811696</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
         <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649747</v>
+        <v>129649733</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439069</v>
+        <v>439097</v>
       </c>
       <c r="R43" t="n">
-        <v>6811626</v>
+        <v>6811705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649733</v>
+        <v>129649738</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439097</v>
+        <v>439156</v>
       </c>
       <c r="R44" t="n">
-        <v>6811705</v>
+        <v>6811648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649738</v>
+        <v>129649747</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439156</v>
+        <v>439069</v>
       </c>
       <c r="R45" t="n">
-        <v>6811648</v>
+        <v>6811626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5004,7 +5004,7 @@
         <v>129649702</v>
       </c>
       <c r="B46" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>129649736</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>129649725</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649697</v>
+        <v>129649728</v>
       </c>
       <c r="B51" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438961</v>
+        <v>438994</v>
       </c>
       <c r="R51" t="n">
-        <v>6811763</v>
+        <v>6811747</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649728</v>
+        <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438994</v>
+        <v>438961</v>
       </c>
       <c r="R52" t="n">
-        <v>6811747</v>
+        <v>6811763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
         <v>129649685</v>
       </c>
       <c r="B53" t="n">
-        <v>56928</v>
+        <v>56929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649732</v>
+        <v>129649671</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439106</v>
+        <v>439129</v>
       </c>
       <c r="R55" t="n">
-        <v>6811690</v>
+        <v>6811570</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5982,7 +5982,7 @@
         <v>129649737</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>129649703</v>
       </c>
       <c r="B57" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649732</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439106</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811690</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
         <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649676</v>
+        <v>129649691</v>
       </c>
       <c r="B60" t="n">
-        <v>57895</v>
+        <v>78834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,42 +6383,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438971</v>
+        <v>439156</v>
       </c>
       <c r="R60" t="n">
-        <v>6811657</v>
+        <v>6811687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6451,11 +6443,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6485,7 +6472,7 @@
         <v>129649664</v>
       </c>
       <c r="B61" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6582,7 +6569,7 @@
         <v>129649754</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6679,7 +6666,7 @@
         <v>129649739</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6773,10 +6760,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649691</v>
+        <v>129649676</v>
       </c>
       <c r="B64" t="n">
-        <v>78833</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,34 +6771,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>439156</v>
+        <v>438971</v>
       </c>
       <c r="R64" t="n">
-        <v>6811687</v>
+        <v>6811657</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6844,6 +6839,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6873,7 +6873,7 @@
         <v>129649696</v>
       </c>
       <c r="B65" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>129649750</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B73" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R74" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7843,7 +7843,7 @@
         <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B79" t="n">
-        <v>79665</v>
+        <v>78833</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R79" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,10 +8325,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660839</v>
+        <v>129660835</v>
       </c>
       <c r="B80" t="n">
-        <v>57735</v>
+        <v>79666</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8336,42 +8336,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438773</v>
+        <v>438807</v>
       </c>
       <c r="R80" t="n">
-        <v>6811783</v>
+        <v>6811845</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,10 +8422,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660855</v>
+        <v>129660839</v>
       </c>
       <c r="B81" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8441,34 +8433,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438795</v>
+        <v>438773</v>
       </c>
       <c r="R81" t="n">
-        <v>6811815</v>
+        <v>6811783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8530,7 +8530,7 @@
         <v>129660841</v>
       </c>
       <c r="B82" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>129660842</v>
       </c>
       <c r="B83" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>129660844</v>
       </c>
       <c r="B87" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649690</v>
+        <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438937</v>
+        <v>439101</v>
       </c>
       <c r="R3" t="n">
-        <v>6811799</v>
+        <v>6811602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649751</v>
+        <v>129649730</v>
       </c>
       <c r="B4" t="n">
         <v>79076</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439101</v>
+        <v>439044</v>
       </c>
       <c r="R4" t="n">
-        <v>6811602</v>
+        <v>6811698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649730</v>
+        <v>129649665</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439044</v>
+        <v>438999</v>
       </c>
       <c r="R5" t="n">
-        <v>6811698</v>
+        <v>6811646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649665</v>
+        <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438999</v>
+        <v>438937</v>
       </c>
       <c r="R6" t="n">
-        <v>6811646</v>
+        <v>6811799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649671</v>
+        <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439129</v>
+        <v>439170</v>
       </c>
       <c r="R55" t="n">
-        <v>6811570</v>
+        <v>6811661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649737</v>
+        <v>129649703</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439170</v>
+        <v>439167</v>
       </c>
       <c r="R56" t="n">
-        <v>6811661</v>
+        <v>6811669</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649703</v>
+        <v>129649732</v>
       </c>
       <c r="B57" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439167</v>
+        <v>439106</v>
       </c>
       <c r="R57" t="n">
-        <v>6811669</v>
+        <v>6811690</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649732</v>
+        <v>129649675</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439106</v>
+        <v>439132</v>
       </c>
       <c r="R58" t="n">
-        <v>6811690</v>
+        <v>6811591</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6244,6 +6244,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6270,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649675</v>
+        <v>129649671</v>
       </c>
       <c r="B59" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439132</v>
+        <v>439129</v>
       </c>
       <c r="R59" t="n">
-        <v>6811591</v>
+        <v>6811570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6341,11 +6346,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649691</v>
+        <v>129649664</v>
       </c>
       <c r="B60" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439156</v>
+        <v>439138</v>
       </c>
       <c r="R60" t="n">
-        <v>6811687</v>
+        <v>6811625</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649664</v>
+        <v>129649754</v>
       </c>
       <c r="B61" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6480,21 +6480,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439138</v>
+        <v>439022</v>
       </c>
       <c r="R61" t="n">
-        <v>6811625</v>
+        <v>6811624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649754</v>
+        <v>129649739</v>
       </c>
       <c r="B62" t="n">
         <v>79076</v>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439022</v>
+        <v>439148</v>
       </c>
       <c r="R62" t="n">
-        <v>6811624</v>
+        <v>6811637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649739</v>
+        <v>129649691</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439148</v>
+        <v>439156</v>
       </c>
       <c r="R63" t="n">
-        <v>6811637</v>
+        <v>6811687</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8325,10 +8325,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660835</v>
+        <v>129660839</v>
       </c>
       <c r="B80" t="n">
-        <v>79666</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8336,34 +8336,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438807</v>
+        <v>438773</v>
       </c>
       <c r="R80" t="n">
-        <v>6811845</v>
+        <v>6811783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8422,10 +8430,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660839</v>
+        <v>129660835</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>79666</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8433,42 +8441,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438773</v>
+        <v>438807</v>
       </c>
       <c r="R81" t="n">
-        <v>6811783</v>
+        <v>6811845</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,42 +8748,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R84" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8842,10 +8834,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8853,34 +8845,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R85" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129649730</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649665</v>
+        <v>129649690</v>
       </c>
       <c r="B5" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438999</v>
+        <v>438937</v>
       </c>
       <c r="R5" t="n">
-        <v>6811646</v>
+        <v>6811799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>438999</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129649729</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129649734</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>129649749</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649693</v>
+        <v>129649700</v>
       </c>
       <c r="B11" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439138</v>
+        <v>438940</v>
       </c>
       <c r="R11" t="n">
-        <v>6811630</v>
+        <v>6811804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649700</v>
+        <v>129649699</v>
       </c>
       <c r="B12" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438940</v>
+        <v>438935</v>
       </c>
       <c r="R12" t="n">
-        <v>6811804</v>
+        <v>6811797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,45 +1750,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649699</v>
+        <v>129649684</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>56929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438935</v>
+        <v>439120</v>
       </c>
       <c r="R13" t="n">
-        <v>6811797</v>
+        <v>6811610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,53 +1855,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649684</v>
+        <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>56929</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439120</v>
+        <v>439138</v>
       </c>
       <c r="R14" t="n">
-        <v>6811610</v>
+        <v>6811630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,45 +2259,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649667</v>
+        <v>129649681</v>
       </c>
       <c r="B18" t="n">
-        <v>79695</v>
+        <v>56929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439072</v>
+        <v>439028</v>
       </c>
       <c r="R18" t="n">
-        <v>6811592</v>
+        <v>6811657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2330,6 +2338,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2359,7 +2372,7 @@
         <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2469,7 @@
         <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2566,7 @@
         <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2647,53 +2660,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649681</v>
+        <v>129649667</v>
       </c>
       <c r="B22" t="n">
-        <v>56929</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439028</v>
+        <v>439072</v>
       </c>
       <c r="R22" t="n">
-        <v>6811657</v>
+        <v>6811592</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2731,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R23" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>129649663</v>
       </c>
       <c r="B26" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>129649756</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129649746</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R32" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B33" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R33" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649740</v>
+        <v>129649666</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439121</v>
+        <v>439131</v>
       </c>
       <c r="R34" t="n">
-        <v>6811628</v>
+        <v>6811582</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3932,7 +3932,7 @@
         <v>129649705</v>
       </c>
       <c r="B35" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649666</v>
+        <v>129649740</v>
       </c>
       <c r="B36" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439131</v>
+        <v>439121</v>
       </c>
       <c r="R36" t="n">
-        <v>6811582</v>
+        <v>6811628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4126,7 +4126,7 @@
         <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R38" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649727</v>
+        <v>129649752</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438945</v>
+        <v>439063</v>
       </c>
       <c r="R39" t="n">
-        <v>6811803</v>
+        <v>6811611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649752</v>
+        <v>129649742</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439063</v>
+        <v>439038</v>
       </c>
       <c r="R40" t="n">
-        <v>6811611</v>
+        <v>6811696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649742</v>
+        <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439038</v>
+        <v>439072</v>
       </c>
       <c r="R41" t="n">
-        <v>6811696</v>
+        <v>6811592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
         <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129649733</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>129649738</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>129649747</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>129649702</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>129649736</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>129649725</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649728</v>
+        <v>129649697</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438994</v>
+        <v>438961</v>
       </c>
       <c r="R51" t="n">
-        <v>6811747</v>
+        <v>6811763</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649697</v>
+        <v>129649728</v>
       </c>
       <c r="B52" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438961</v>
+        <v>438994</v>
       </c>
       <c r="R52" t="n">
-        <v>6811763</v>
+        <v>6811747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129649703</v>
       </c>
       <c r="B56" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>129649732</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649675</v>
+        <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439132</v>
+        <v>439129</v>
       </c>
       <c r="R58" t="n">
-        <v>6811591</v>
+        <v>6811570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6244,11 +6244,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6275,10 +6270,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649671</v>
+        <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6286,21 +6281,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439129</v>
+        <v>439132</v>
       </c>
       <c r="R59" t="n">
-        <v>6811570</v>
+        <v>6811591</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6346,6 +6341,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649664</v>
+        <v>129649754</v>
       </c>
       <c r="B60" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439138</v>
+        <v>439022</v>
       </c>
       <c r="R60" t="n">
-        <v>6811625</v>
+        <v>6811624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649754</v>
+        <v>129649739</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439022</v>
+        <v>439148</v>
       </c>
       <c r="R61" t="n">
-        <v>6811624</v>
+        <v>6811637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649739</v>
+        <v>129649664</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439148</v>
+        <v>439138</v>
       </c>
       <c r="R62" t="n">
-        <v>6811637</v>
+        <v>6811625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649691</v>
+        <v>129649676</v>
       </c>
       <c r="B63" t="n">
-        <v>78834</v>
+        <v>57896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,34 +6674,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439156</v>
+        <v>438971</v>
       </c>
       <c r="R63" t="n">
-        <v>6811687</v>
+        <v>6811657</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6734,6 +6742,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6760,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649676</v>
+        <v>129649691</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6771,42 +6784,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438971</v>
+        <v>439156</v>
       </c>
       <c r="R64" t="n">
-        <v>6811657</v>
+        <v>6811687</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6839,11 +6844,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6873,7 +6873,7 @@
         <v>129649696</v>
       </c>
       <c r="B65" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>129649750</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>78839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R73" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B74" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R74" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7843,7 +7843,7 @@
         <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>129660855</v>
       </c>
       <c r="B79" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8325,32 +8325,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660839</v>
+        <v>129660841</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438773</v>
+        <v>438785</v>
       </c>
       <c r="R80" t="n">
-        <v>6811783</v>
+        <v>6811874</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660835</v>
+        <v>129660839</v>
       </c>
       <c r="B81" t="n">
-        <v>79666</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8441,34 +8441,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438807</v>
+        <v>438773</v>
       </c>
       <c r="R81" t="n">
-        <v>6811845</v>
+        <v>6811783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8527,53 +8535,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660841</v>
+        <v>129660835</v>
       </c>
       <c r="B82" t="n">
-        <v>56926</v>
+        <v>79671</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438785</v>
+        <v>438807</v>
       </c>
       <c r="R82" t="n">
-        <v>6811874</v>
+        <v>6811845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,34 +8748,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R84" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8834,10 +8842,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8845,42 +8853,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R85" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>91614</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,34 +8950,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R86" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9018,6 +9025,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9036,10 +9044,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B87" t="n">
-        <v>91609</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9047,41 +9055,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R87" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9122,7 +9123,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -2369,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649701</v>
+        <v>129649744</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2380,21 +2380,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439071</v>
+        <v>438987</v>
       </c>
       <c r="R19" t="n">
-        <v>6811718</v>
+        <v>6811668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649704</v>
+        <v>129649667</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,21 +2477,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439142</v>
+        <v>439072</v>
       </c>
       <c r="R20" t="n">
-        <v>6811627</v>
+        <v>6811592</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649744</v>
+        <v>129649701</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438987</v>
+        <v>439071</v>
       </c>
       <c r="R21" t="n">
-        <v>6811668</v>
+        <v>6811718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649667</v>
+        <v>129649704</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439072</v>
+        <v>439142</v>
       </c>
       <c r="R22" t="n">
-        <v>6811592</v>
+        <v>6811627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R23" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649692</v>
+        <v>129649741</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439167</v>
+        <v>439100</v>
       </c>
       <c r="R25" t="n">
-        <v>6811669</v>
+        <v>6811652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R32" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R33" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R34" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649688</v>
+        <v>129649666</v>
       </c>
       <c r="B37" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438959</v>
+        <v>439131</v>
       </c>
       <c r="R37" t="n">
-        <v>6811760</v>
+        <v>6811582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R38" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649677</v>
+        <v>129649747</v>
       </c>
       <c r="B42" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439053</v>
+        <v>439069</v>
       </c>
       <c r="R42" t="n">
-        <v>6811673</v>
+        <v>6811626</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4710,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649733</v>
+        <v>129649677</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439097</v>
+        <v>439053</v>
       </c>
       <c r="R43" t="n">
-        <v>6811705</v>
+        <v>6811673</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4781,6 +4776,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,7 +4807,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649738</v>
+        <v>129649733</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439156</v>
+        <v>439097</v>
       </c>
       <c r="R44" t="n">
-        <v>6811648</v>
+        <v>6811705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,7 +4904,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649747</v>
+        <v>129649738</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439069</v>
+        <v>439156</v>
       </c>
       <c r="R45" t="n">
-        <v>6811626</v>
+        <v>6811648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649737</v>
+        <v>129649675</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439170</v>
+        <v>439132</v>
       </c>
       <c r="R55" t="n">
-        <v>6811661</v>
+        <v>6811591</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5953,6 +5953,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5979,10 +5984,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649703</v>
+        <v>129649737</v>
       </c>
       <c r="B56" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5995,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439167</v>
+        <v>439170</v>
       </c>
       <c r="R56" t="n">
-        <v>6811669</v>
+        <v>6811661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6173,10 +6178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649703</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6189,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439167</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811669</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6270,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649675</v>
+        <v>129649671</v>
       </c>
       <c r="B59" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439132</v>
+        <v>439129</v>
       </c>
       <c r="R59" t="n">
-        <v>6811591</v>
+        <v>6811570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6341,11 +6346,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649754</v>
+        <v>129649664</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439022</v>
+        <v>439138</v>
       </c>
       <c r="R60" t="n">
-        <v>6811624</v>
+        <v>6811625</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R61" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649664</v>
+        <v>129649739</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439138</v>
+        <v>439148</v>
       </c>
       <c r="R62" t="n">
-        <v>6811625</v>
+        <v>6811637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649696</v>
+        <v>129649672</v>
       </c>
       <c r="B65" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R65" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649750</v>
+        <v>129649687</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R66" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649672</v>
+        <v>129649750</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438973</v>
+        <v>439104</v>
       </c>
       <c r="R67" t="n">
-        <v>6811633</v>
+        <v>6811588</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649687</v>
+        <v>129649696</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660856</v>
       </c>
       <c r="B73" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438810</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811833</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B75" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R75" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8325,32 +8325,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B80" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R80" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,32 +8430,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660839</v>
+        <v>129660841</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438773</v>
+        <v>438785</v>
       </c>
       <c r="R81" t="n">
-        <v>6811783</v>
+        <v>6811874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,42 +8748,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R84" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8842,10 +8834,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8853,34 +8845,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R85" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,41 +8950,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R86" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9025,7 +9018,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9044,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660890</v>
+        <v>129660836</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,21 +9047,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9079,10 +9071,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438796</v>
+        <v>438795</v>
       </c>
       <c r="R87" t="n">
-        <v>6811854</v>
+        <v>6811868</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9141,10 +9133,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660836</v>
+        <v>129660844</v>
       </c>
       <c r="B88" t="n">
-        <v>79671</v>
+        <v>91614</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,34 +9144,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438795</v>
+        <v>438831</v>
       </c>
       <c r="R88" t="n">
-        <v>6811868</v>
+        <v>6811826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9220,6 +9219,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R3" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649730</v>
+        <v>129649751</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439044</v>
+        <v>439101</v>
       </c>
       <c r="R4" t="n">
-        <v>6811698</v>
+        <v>6811602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R5" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649665</v>
+        <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438999</v>
+        <v>438937</v>
       </c>
       <c r="R6" t="n">
-        <v>6811646</v>
+        <v>6811799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1952,45 +1952,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129649735</v>
+        <v>129649683</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439148</v>
+        <v>439106</v>
       </c>
       <c r="R15" t="n">
-        <v>6811695</v>
+        <v>6811611</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,53 +2162,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649683</v>
+        <v>129649735</v>
       </c>
       <c r="B17" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439106</v>
+        <v>439148</v>
       </c>
       <c r="R17" t="n">
-        <v>6811611</v>
+        <v>6811695</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,53 +2259,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649681</v>
+        <v>129649744</v>
       </c>
       <c r="B18" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439028</v>
+        <v>438987</v>
       </c>
       <c r="R18" t="n">
-        <v>6811657</v>
+        <v>6811668</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,11 +2330,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2369,45 +2356,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649744</v>
+        <v>129649681</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438987</v>
+        <v>439028</v>
       </c>
       <c r="R19" t="n">
-        <v>6811668</v>
+        <v>6811657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2440,6 +2435,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649692</v>
+        <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439167</v>
+        <v>439020</v>
       </c>
       <c r="R23" t="n">
-        <v>6811669</v>
+        <v>6811728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R25" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649756</v>
+        <v>129649746</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438993</v>
+        <v>439029</v>
       </c>
       <c r="R27" t="n">
-        <v>6811613</v>
+        <v>6811655</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649746</v>
+        <v>129649756</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439029</v>
+        <v>438993</v>
       </c>
       <c r="R28" t="n">
-        <v>6811655</v>
+        <v>6811613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649743</v>
+        <v>129649731</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438992</v>
+        <v>439095</v>
       </c>
       <c r="R30" t="n">
-        <v>6811688</v>
+        <v>6811729</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129649731</v>
+        <v>129649743</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439095</v>
+        <v>438992</v>
       </c>
       <c r="R31" t="n">
-        <v>6811729</v>
+        <v>6811688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R32" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R33" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649688</v>
+        <v>129649740</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438959</v>
+        <v>439121</v>
       </c>
       <c r="R34" t="n">
-        <v>6811760</v>
+        <v>6811628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649705</v>
+        <v>129649688</v>
       </c>
       <c r="B35" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439072</v>
+        <v>438959</v>
       </c>
       <c r="R35" t="n">
-        <v>6811591</v>
+        <v>6811760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649740</v>
+        <v>129649705</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439121</v>
+        <v>439072</v>
       </c>
       <c r="R36" t="n">
-        <v>6811628</v>
+        <v>6811591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R38" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R41" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649747</v>
+        <v>129649736</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439069</v>
+        <v>439165</v>
       </c>
       <c r="R42" t="n">
-        <v>6811626</v>
+        <v>6811686</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4705,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649677</v>
+        <v>129649725</v>
       </c>
       <c r="B43" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439053</v>
+        <v>438962</v>
       </c>
       <c r="R43" t="n">
-        <v>6811673</v>
+        <v>6811761</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4776,11 +4776,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,10 +4802,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649733</v>
+        <v>129649702</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,21 +4813,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439097</v>
+        <v>439157</v>
       </c>
       <c r="R44" t="n">
-        <v>6811705</v>
+        <v>6811682</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649738</v>
+        <v>129649677</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439156</v>
+        <v>439053</v>
       </c>
       <c r="R45" t="n">
-        <v>6811648</v>
+        <v>6811673</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4975,6 +4970,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649702</v>
+        <v>129649733</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439157</v>
+        <v>439097</v>
       </c>
       <c r="R46" t="n">
-        <v>6811682</v>
+        <v>6811705</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649736</v>
+        <v>129649738</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439165</v>
+        <v>439156</v>
       </c>
       <c r="R47" t="n">
-        <v>6811686</v>
+        <v>6811648</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,7 +5195,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649725</v>
+        <v>129649747</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438962</v>
+        <v>439069</v>
       </c>
       <c r="R48" t="n">
-        <v>6811761</v>
+        <v>6811626</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129649753</v>
+        <v>129649745</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439024</v>
+        <v>438975</v>
       </c>
       <c r="R49" t="n">
-        <v>6811608</v>
+        <v>6811649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129649745</v>
+        <v>129649753</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438975</v>
+        <v>439024</v>
       </c>
       <c r="R50" t="n">
-        <v>6811649</v>
+        <v>6811608</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5486,45 +5486,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649697</v>
+        <v>129649685</v>
       </c>
       <c r="B51" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438961</v>
+        <v>439104</v>
       </c>
       <c r="R51" t="n">
-        <v>6811763</v>
+        <v>6811591</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5583,10 +5591,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649728</v>
+        <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5594,21 +5602,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5618,10 +5626,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438994</v>
+        <v>438961</v>
       </c>
       <c r="R52" t="n">
-        <v>6811747</v>
+        <v>6811763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5680,53 +5688,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649685</v>
+        <v>129649728</v>
       </c>
       <c r="B53" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>439104</v>
+        <v>438994</v>
       </c>
       <c r="R53" t="n">
-        <v>6811591</v>
+        <v>6811747</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B55" t="n">
-        <v>57896</v>
+        <v>78838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R55" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5953,11 +5953,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6178,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6189,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R58" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6275,10 +6270,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649671</v>
+        <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6286,21 +6281,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439129</v>
+        <v>439132</v>
       </c>
       <c r="R59" t="n">
-        <v>6811570</v>
+        <v>6811591</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6346,6 +6341,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6469,7 +6469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649754</v>
+        <v>129649739</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439022</v>
+        <v>439148</v>
       </c>
       <c r="R61" t="n">
-        <v>6811624</v>
+        <v>6811637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R62" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649672</v>
+        <v>129649696</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R65" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649687</v>
+        <v>129649750</v>
       </c>
       <c r="B66" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R66" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649750</v>
+        <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>439104</v>
+        <v>438973</v>
       </c>
       <c r="R67" t="n">
-        <v>6811588</v>
+        <v>6811633</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649696</v>
+        <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R73" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660885</v>
+        <v>129660856</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438717</v>
+        <v>438810</v>
       </c>
       <c r="R74" t="n">
-        <v>6811848</v>
+        <v>6811833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B75" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R75" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8325,32 +8325,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660839</v>
+        <v>129660841</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438773</v>
+        <v>438785</v>
       </c>
       <c r="R80" t="n">
-        <v>6811783</v>
+        <v>6811874</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,32 +8430,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B81" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R81" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,34 +8748,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R84" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8834,10 +8842,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8845,42 +8853,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R85" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,34 +8950,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R86" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9018,6 +9025,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9036,10 +9044,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660836</v>
+        <v>129660890</v>
       </c>
       <c r="B87" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9047,21 +9055,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9071,10 +9079,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438795</v>
+        <v>438796</v>
       </c>
       <c r="R87" t="n">
-        <v>6811868</v>
+        <v>6811854</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9133,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660844</v>
+        <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>91614</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9144,41 +9152,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438831</v>
+        <v>438795</v>
       </c>
       <c r="R88" t="n">
-        <v>6811826</v>
+        <v>6811868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9219,7 +9220,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649665</v>
+        <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438999</v>
+        <v>439101</v>
       </c>
       <c r="R3" t="n">
-        <v>6811646</v>
+        <v>6811602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649751</v>
+        <v>129649730</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439101</v>
+        <v>439044</v>
       </c>
       <c r="R4" t="n">
-        <v>6811602</v>
+        <v>6811698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649730</v>
+        <v>129649690</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439044</v>
+        <v>438937</v>
       </c>
       <c r="R5" t="n">
-        <v>6811698</v>
+        <v>6811799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>438999</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1750,53 +1750,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649684</v>
+        <v>129649693</v>
       </c>
       <c r="B13" t="n">
-        <v>56929</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439120</v>
+        <v>439138</v>
       </c>
       <c r="R13" t="n">
-        <v>6811610</v>
+        <v>6811630</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,45 +1847,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649693</v>
+        <v>129649684</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>56929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439138</v>
+        <v>439120</v>
       </c>
       <c r="R14" t="n">
-        <v>6811630</v>
+        <v>6811610</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2356,53 +2356,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649681</v>
+        <v>129649667</v>
       </c>
       <c r="B19" t="n">
-        <v>56929</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439028</v>
+        <v>439072</v>
       </c>
       <c r="R19" t="n">
-        <v>6811657</v>
+        <v>6811592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,11 +2427,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2466,10 +2453,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649667</v>
+        <v>129649701</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,21 +2464,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2501,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439072</v>
+        <v>439071</v>
       </c>
       <c r="R20" t="n">
-        <v>6811592</v>
+        <v>6811718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,7 +2550,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649701</v>
+        <v>129649704</v>
       </c>
       <c r="B21" t="n">
         <v>78838</v>
@@ -2598,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439071</v>
+        <v>439142</v>
       </c>
       <c r="R21" t="n">
-        <v>6811718</v>
+        <v>6811627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2660,45 +2647,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649704</v>
+        <v>129649681</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439142</v>
+        <v>439028</v>
       </c>
       <c r="R22" t="n">
-        <v>6811627</v>
+        <v>6811657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R23" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649663</v>
+        <v>129649756</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439158</v>
+        <v>438993</v>
       </c>
       <c r="R26" t="n">
-        <v>6811692</v>
+        <v>6811613</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649756</v>
+        <v>129649663</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438993</v>
+        <v>439158</v>
       </c>
       <c r="R28" t="n">
-        <v>6811613</v>
+        <v>6811692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649731</v>
+        <v>129649743</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439095</v>
+        <v>438992</v>
       </c>
       <c r="R30" t="n">
-        <v>6811729</v>
+        <v>6811688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129649743</v>
+        <v>129649731</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438992</v>
+        <v>439095</v>
       </c>
       <c r="R31" t="n">
-        <v>6811688</v>
+        <v>6811729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R32" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R33" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649740</v>
+        <v>129649688</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439121</v>
+        <v>438959</v>
       </c>
       <c r="R34" t="n">
-        <v>6811628</v>
+        <v>6811760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649688</v>
+        <v>129649740</v>
       </c>
       <c r="B35" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438959</v>
+        <v>439121</v>
       </c>
       <c r="R35" t="n">
-        <v>6811760</v>
+        <v>6811628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649736</v>
+        <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439165</v>
+        <v>439053</v>
       </c>
       <c r="R42" t="n">
-        <v>6811686</v>
+        <v>6811673</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4679,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,7 +4710,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649725</v>
+        <v>129649733</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438962</v>
+        <v>439097</v>
       </c>
       <c r="R43" t="n">
-        <v>6811761</v>
+        <v>6811705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4802,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649702</v>
+        <v>129649738</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4818,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439157</v>
+        <v>439156</v>
       </c>
       <c r="R44" t="n">
-        <v>6811682</v>
+        <v>6811648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649677</v>
+        <v>129649747</v>
       </c>
       <c r="B45" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4915,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439053</v>
+        <v>439069</v>
       </c>
       <c r="R45" t="n">
-        <v>6811673</v>
+        <v>6811626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4970,11 +4975,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5001,7 +5001,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649733</v>
+        <v>129649736</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439097</v>
+        <v>439165</v>
       </c>
       <c r="R46" t="n">
-        <v>6811705</v>
+        <v>6811686</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649738</v>
+        <v>129649725</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439156</v>
+        <v>438962</v>
       </c>
       <c r="R47" t="n">
-        <v>6811648</v>
+        <v>6811761</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649747</v>
+        <v>129649702</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439069</v>
+        <v>439157</v>
       </c>
       <c r="R48" t="n">
-        <v>6811626</v>
+        <v>6811682</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129649745</v>
+        <v>129649753</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5327,10 +5327,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438975</v>
+        <v>439024</v>
       </c>
       <c r="R49" t="n">
-        <v>6811649</v>
+        <v>6811608</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129649753</v>
+        <v>129649745</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439024</v>
+        <v>438975</v>
       </c>
       <c r="R50" t="n">
-        <v>6811608</v>
+        <v>6811649</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5486,53 +5486,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649685</v>
+        <v>129649728</v>
       </c>
       <c r="B51" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439104</v>
+        <v>438994</v>
       </c>
       <c r="R51" t="n">
-        <v>6811591</v>
+        <v>6811747</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5591,45 +5583,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649697</v>
+        <v>129649685</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438961</v>
+        <v>439104</v>
       </c>
       <c r="R52" t="n">
-        <v>6811763</v>
+        <v>6811591</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649728</v>
+        <v>129649697</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438994</v>
+        <v>438961</v>
       </c>
       <c r="R53" t="n">
-        <v>6811747</v>
+        <v>6811763</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649703</v>
+        <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439167</v>
+        <v>439170</v>
       </c>
       <c r="R55" t="n">
-        <v>6811669</v>
+        <v>6811661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,7 +5979,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649737</v>
+        <v>129649732</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439170</v>
+        <v>439106</v>
       </c>
       <c r="R56" t="n">
-        <v>6811661</v>
+        <v>6811690</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649732</v>
+        <v>129649671</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439106</v>
+        <v>439129</v>
       </c>
       <c r="R57" t="n">
-        <v>6811690</v>
+        <v>6811570</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649703</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439167</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811669</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649664</v>
+        <v>129649754</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439138</v>
+        <v>439022</v>
       </c>
       <c r="R60" t="n">
-        <v>6811625</v>
+        <v>6811624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649754</v>
+        <v>129649664</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439022</v>
+        <v>439138</v>
       </c>
       <c r="R62" t="n">
-        <v>6811624</v>
+        <v>6811625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649696</v>
+        <v>129649750</v>
       </c>
       <c r="B65" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R65" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649750</v>
+        <v>129649696</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R66" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B73" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B74" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R74" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660885</v>
+        <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438717</v>
+        <v>438810</v>
       </c>
       <c r="R75" t="n">
-        <v>6811848</v>
+        <v>6811833</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R3" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649730</v>
+        <v>129649751</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439044</v>
+        <v>439101</v>
       </c>
       <c r="R4" t="n">
-        <v>6811698</v>
+        <v>6811602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R5" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649665</v>
+        <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438999</v>
+        <v>438937</v>
       </c>
       <c r="R6" t="n">
-        <v>6811646</v>
+        <v>6811799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1556,45 +1556,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649700</v>
+        <v>129649684</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438940</v>
+        <v>439120</v>
       </c>
       <c r="R11" t="n">
-        <v>6811804</v>
+        <v>6811610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649699</v>
+        <v>129649693</v>
       </c>
       <c r="B12" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438935</v>
+        <v>439138</v>
       </c>
       <c r="R12" t="n">
-        <v>6811797</v>
+        <v>6811630</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649693</v>
+        <v>129649700</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439138</v>
+        <v>438940</v>
       </c>
       <c r="R13" t="n">
-        <v>6811630</v>
+        <v>6811804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,53 +1855,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649684</v>
+        <v>129649699</v>
       </c>
       <c r="B14" t="n">
-        <v>56929</v>
+        <v>78838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439120</v>
+        <v>438935</v>
       </c>
       <c r="R14" t="n">
-        <v>6811610</v>
+        <v>6811797</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649744</v>
+        <v>129649667</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438987</v>
+        <v>439072</v>
       </c>
       <c r="R18" t="n">
-        <v>6811668</v>
+        <v>6811592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649667</v>
+        <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2367,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439072</v>
+        <v>439071</v>
       </c>
       <c r="R19" t="n">
-        <v>6811592</v>
+        <v>6811718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649701</v>
+        <v>129649704</v>
       </c>
       <c r="B20" t="n">
         <v>78838</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439071</v>
+        <v>439142</v>
       </c>
       <c r="R20" t="n">
-        <v>6811718</v>
+        <v>6811627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649704</v>
+        <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2561,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439142</v>
+        <v>438987</v>
       </c>
       <c r="R21" t="n">
-        <v>6811627</v>
+        <v>6811668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R23" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649692</v>
+        <v>129649741</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439167</v>
+        <v>439100</v>
       </c>
       <c r="R25" t="n">
-        <v>6811669</v>
+        <v>6811652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649756</v>
+        <v>129649663</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438993</v>
+        <v>439158</v>
       </c>
       <c r="R26" t="n">
-        <v>6811613</v>
+        <v>6811692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,45 +3145,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649746</v>
+        <v>129649679</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439029</v>
+        <v>439074</v>
       </c>
       <c r="R27" t="n">
-        <v>6811655</v>
+        <v>6811666</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649663</v>
+        <v>129649756</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3261,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3285,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439158</v>
+        <v>438993</v>
       </c>
       <c r="R28" t="n">
-        <v>6811692</v>
+        <v>6811613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,53 +3347,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649679</v>
+        <v>129649746</v>
       </c>
       <c r="B29" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439074</v>
+        <v>439029</v>
       </c>
       <c r="R29" t="n">
-        <v>6811666</v>
+        <v>6811655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R32" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R33" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R38" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649752</v>
+        <v>129649727</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439063</v>
+        <v>438945</v>
       </c>
       <c r="R39" t="n">
-        <v>6811611</v>
+        <v>6811803</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649742</v>
+        <v>129649752</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439038</v>
+        <v>439063</v>
       </c>
       <c r="R40" t="n">
-        <v>6811696</v>
+        <v>6811611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649742</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>439038</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811696</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
         <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649737</v>
+        <v>129649703</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439170</v>
+        <v>439167</v>
       </c>
       <c r="R55" t="n">
-        <v>6811661</v>
+        <v>6811669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,7 +5979,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649732</v>
+        <v>129649737</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439106</v>
+        <v>439170</v>
       </c>
       <c r="R56" t="n">
-        <v>6811690</v>
+        <v>6811661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649671</v>
+        <v>129649732</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439129</v>
+        <v>439106</v>
       </c>
       <c r="R57" t="n">
-        <v>6811570</v>
+        <v>6811690</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R58" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649664</v>
+        <v>129649676</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,34 +6577,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439138</v>
+        <v>438971</v>
       </c>
       <c r="R62" t="n">
-        <v>6811625</v>
+        <v>6811657</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6637,6 +6645,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6663,10 +6676,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649676</v>
+        <v>129649691</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>78839</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,42 +6687,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438971</v>
+        <v>439156</v>
       </c>
       <c r="R63" t="n">
-        <v>6811657</v>
+        <v>6811687</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6742,11 +6747,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6773,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649691</v>
+        <v>129649664</v>
       </c>
       <c r="B64" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,21 +6784,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>439156</v>
+        <v>439138</v>
       </c>
       <c r="R64" t="n">
-        <v>6811687</v>
+        <v>6811625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649696</v>
+        <v>129649687</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649672</v>
+        <v>129649696</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R67" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649687</v>
+        <v>129649672</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R68" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660848</v>
+        <v>129660856</v>
       </c>
       <c r="B74" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438790</v>
+        <v>438810</v>
       </c>
       <c r="R74" t="n">
-        <v>6811814</v>
+        <v>6811833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B75" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R75" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660855</v>
+        <v>129660835</v>
       </c>
       <c r="B79" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438795</v>
+        <v>438807</v>
       </c>
       <c r="R79" t="n">
-        <v>6811815</v>
+        <v>6811845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B82" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8546,21 +8546,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R82" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660844</v>
+        <v>129660836</v>
       </c>
       <c r="B86" t="n">
-        <v>91614</v>
+        <v>79671</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,41 +8950,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438831</v>
+        <v>438795</v>
       </c>
       <c r="R86" t="n">
-        <v>6811826</v>
+        <v>6811868</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9025,7 +9018,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9044,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,34 +9047,41 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R87" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9123,6 +9122,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9141,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660836</v>
+        <v>129660890</v>
       </c>
       <c r="B88" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,21 +9152,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438795</v>
+        <v>438796</v>
       </c>
       <c r="R88" t="n">
-        <v>6811868</v>
+        <v>6811854</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649665</v>
+        <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438999</v>
+        <v>439101</v>
       </c>
       <c r="R3" t="n">
-        <v>6811646</v>
+        <v>6811602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649751</v>
+        <v>129649730</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439101</v>
+        <v>439044</v>
       </c>
       <c r="R4" t="n">
-        <v>6811602</v>
+        <v>6811698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649730</v>
+        <v>129649665</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439044</v>
+        <v>438999</v>
       </c>
       <c r="R5" t="n">
-        <v>6811698</v>
+        <v>6811646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1556,53 +1556,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649684</v>
+        <v>129649700</v>
       </c>
       <c r="B11" t="n">
-        <v>56929</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439120</v>
+        <v>438940</v>
       </c>
       <c r="R11" t="n">
-        <v>6811610</v>
+        <v>6811804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649693</v>
+        <v>129649699</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439138</v>
+        <v>438935</v>
       </c>
       <c r="R12" t="n">
-        <v>6811630</v>
+        <v>6811797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,45 +1750,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649700</v>
+        <v>129649684</v>
       </c>
       <c r="B13" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438940</v>
+        <v>439120</v>
       </c>
       <c r="R13" t="n">
-        <v>6811804</v>
+        <v>6811610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649699</v>
+        <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438935</v>
+        <v>439138</v>
       </c>
       <c r="R14" t="n">
-        <v>6811797</v>
+        <v>6811630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,53 +1952,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129649683</v>
+        <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439106</v>
+        <v>439148</v>
       </c>
       <c r="R15" t="n">
-        <v>6811611</v>
+        <v>6811695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,45 +2154,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649735</v>
+        <v>129649683</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439148</v>
+        <v>439106</v>
       </c>
       <c r="R17" t="n">
-        <v>6811695</v>
+        <v>6811611</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,45 +2259,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649667</v>
+        <v>129649681</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>56929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439072</v>
+        <v>439028</v>
       </c>
       <c r="R18" t="n">
-        <v>6811592</v>
+        <v>6811657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2330,6 +2338,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2356,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649701</v>
+        <v>129649667</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2380,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439071</v>
+        <v>439072</v>
       </c>
       <c r="R19" t="n">
-        <v>6811718</v>
+        <v>6811592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,7 +2466,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649704</v>
+        <v>129649701</v>
       </c>
       <c r="B20" t="n">
         <v>78838</v>
@@ -2488,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439142</v>
+        <v>439071</v>
       </c>
       <c r="R20" t="n">
-        <v>6811627</v>
+        <v>6811718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649744</v>
+        <v>129649704</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2561,21 +2574,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438987</v>
+        <v>439142</v>
       </c>
       <c r="R21" t="n">
-        <v>6811668</v>
+        <v>6811627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,53 +2660,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649681</v>
+        <v>129649744</v>
       </c>
       <c r="B22" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439028</v>
+        <v>438987</v>
       </c>
       <c r="R22" t="n">
-        <v>6811657</v>
+        <v>6811668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2731,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649692</v>
+        <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439167</v>
+        <v>439100</v>
       </c>
       <c r="R23" t="n">
-        <v>6811669</v>
+        <v>6811652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R25" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,45 +3048,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649663</v>
+        <v>129649679</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>56929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439158</v>
+        <v>439074</v>
       </c>
       <c r="R26" t="n">
-        <v>6811692</v>
+        <v>6811666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,53 +3153,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649679</v>
+        <v>129649663</v>
       </c>
       <c r="B27" t="n">
-        <v>56929</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439074</v>
+        <v>439158</v>
       </c>
       <c r="R27" t="n">
-        <v>6811666</v>
+        <v>6811692</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R32" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R33" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649688</v>
+        <v>129649705</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438959</v>
+        <v>439072</v>
       </c>
       <c r="R34" t="n">
-        <v>6811760</v>
+        <v>6811591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649705</v>
+        <v>129649666</v>
       </c>
       <c r="B36" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439072</v>
+        <v>439131</v>
       </c>
       <c r="R36" t="n">
-        <v>6811591</v>
+        <v>6811582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R37" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649677</v>
+        <v>129649733</v>
       </c>
       <c r="B42" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439053</v>
+        <v>439097</v>
       </c>
       <c r="R42" t="n">
-        <v>6811673</v>
+        <v>6811705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4710,7 +4705,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649733</v>
+        <v>129649738</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439097</v>
+        <v>439156</v>
       </c>
       <c r="R43" t="n">
-        <v>6811705</v>
+        <v>6811648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,7 +4802,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649738</v>
+        <v>129649747</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -4842,10 +4837,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439156</v>
+        <v>439069</v>
       </c>
       <c r="R44" t="n">
-        <v>6811648</v>
+        <v>6811626</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4899,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649747</v>
+        <v>129649702</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,21 +4910,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4934,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439069</v>
+        <v>439157</v>
       </c>
       <c r="R45" t="n">
-        <v>6811626</v>
+        <v>6811682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,10 +5190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649702</v>
+        <v>129649677</v>
       </c>
       <c r="B48" t="n">
-        <v>78838</v>
+        <v>91620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,21 +5201,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439157</v>
+        <v>439053</v>
       </c>
       <c r="R48" t="n">
-        <v>6811682</v>
+        <v>6811673</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5266,6 +5261,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5486,45 +5486,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649728</v>
+        <v>129649685</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438994</v>
+        <v>439104</v>
       </c>
       <c r="R51" t="n">
-        <v>6811747</v>
+        <v>6811591</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5583,53 +5591,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649685</v>
+        <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>56929</v>
+        <v>78838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>439104</v>
+        <v>438961</v>
       </c>
       <c r="R52" t="n">
-        <v>6811591</v>
+        <v>6811763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649697</v>
+        <v>129649728</v>
       </c>
       <c r="B53" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5699,21 +5699,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438961</v>
+        <v>438994</v>
       </c>
       <c r="R53" t="n">
-        <v>6811763</v>
+        <v>6811747</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B55" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R55" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649737</v>
+        <v>129649675</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439170</v>
+        <v>439132</v>
       </c>
       <c r="R56" t="n">
-        <v>6811661</v>
+        <v>6811591</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6050,6 +6050,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6076,7 +6081,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649732</v>
+        <v>129649737</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439106</v>
+        <v>439170</v>
       </c>
       <c r="R57" t="n">
-        <v>6811690</v>
+        <v>6811661</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6173,10 +6178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649703</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6189,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439167</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811669</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6270,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649675</v>
+        <v>129649732</v>
       </c>
       <c r="B59" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439132</v>
+        <v>439106</v>
       </c>
       <c r="R59" t="n">
-        <v>6811591</v>
+        <v>6811690</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6341,11 +6346,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649754</v>
+        <v>129649664</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439022</v>
+        <v>439138</v>
       </c>
       <c r="R60" t="n">
-        <v>6811624</v>
+        <v>6811625</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R61" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649676</v>
+        <v>129649739</v>
       </c>
       <c r="B62" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,42 +6577,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438971</v>
+        <v>439148</v>
       </c>
       <c r="R62" t="n">
-        <v>6811657</v>
+        <v>6811637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6645,11 +6637,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6773,10 +6760,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649664</v>
+        <v>129649676</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,34 +6771,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>439138</v>
+        <v>438971</v>
       </c>
       <c r="R64" t="n">
-        <v>6811625</v>
+        <v>6811657</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6844,6 +6839,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649750</v>
+        <v>129649672</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>439104</v>
+        <v>438973</v>
       </c>
       <c r="R65" t="n">
-        <v>6811588</v>
+        <v>6811633</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649672</v>
+        <v>129649750</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438973</v>
+        <v>439104</v>
       </c>
       <c r="R68" t="n">
-        <v>6811633</v>
+        <v>6811588</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B79" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R79" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,53 +8325,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660841</v>
+        <v>129660835</v>
       </c>
       <c r="B80" t="n">
-        <v>56926</v>
+        <v>79671</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438785</v>
+        <v>438807</v>
       </c>
       <c r="R80" t="n">
-        <v>6811874</v>
+        <v>6811845</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8535,45 +8527,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660855</v>
+        <v>129660841</v>
       </c>
       <c r="B82" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438795</v>
+        <v>438785</v>
       </c>
       <c r="R82" t="n">
-        <v>6811815</v>
+        <v>6811874</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,42 +8748,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R84" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8842,10 +8834,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8853,34 +8845,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R85" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660836</v>
+        <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>79671</v>
+        <v>91620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,34 +8950,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438795</v>
+        <v>438831</v>
       </c>
       <c r="R86" t="n">
-        <v>6811868</v>
+        <v>6811826</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9018,6 +9025,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9036,10 +9044,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B87" t="n">
-        <v>91618</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9047,41 +9055,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R87" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9122,7 +9123,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9141,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660890</v>
+        <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,21 +9152,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438796</v>
+        <v>438795</v>
       </c>
       <c r="R88" t="n">
-        <v>6811854</v>
+        <v>6811868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R3" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649730</v>
+        <v>129649690</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439044</v>
+        <v>438937</v>
       </c>
       <c r="R4" t="n">
-        <v>6811698</v>
+        <v>6811799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649665</v>
+        <v>129649751</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438999</v>
+        <v>439101</v>
       </c>
       <c r="R5" t="n">
-        <v>6811646</v>
+        <v>6811602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3048,53 +3048,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649679</v>
+        <v>129649663</v>
       </c>
       <c r="B26" t="n">
-        <v>56929</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439074</v>
+        <v>439158</v>
       </c>
       <c r="R26" t="n">
-        <v>6811666</v>
+        <v>6811692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,10 +3145,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649663</v>
+        <v>129649756</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3164,21 +3156,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3188,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439158</v>
+        <v>438993</v>
       </c>
       <c r="R27" t="n">
-        <v>6811692</v>
+        <v>6811613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,7 +3242,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649756</v>
+        <v>129649746</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3285,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438993</v>
+        <v>439029</v>
       </c>
       <c r="R28" t="n">
-        <v>6811613</v>
+        <v>6811655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,45 +3339,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649746</v>
+        <v>129649679</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439029</v>
+        <v>439074</v>
       </c>
       <c r="R29" t="n">
-        <v>6811655</v>
+        <v>6811666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649705</v>
+        <v>129649688</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439072</v>
+        <v>438959</v>
       </c>
       <c r="R34" t="n">
-        <v>6811591</v>
+        <v>6811760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649740</v>
+        <v>129649705</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439121</v>
+        <v>439072</v>
       </c>
       <c r="R35" t="n">
-        <v>6811628</v>
+        <v>6811591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649666</v>
+        <v>129649740</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439131</v>
+        <v>439121</v>
       </c>
       <c r="R36" t="n">
-        <v>6811582</v>
+        <v>6811628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649688</v>
+        <v>129649666</v>
       </c>
       <c r="B37" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438959</v>
+        <v>439131</v>
       </c>
       <c r="R37" t="n">
-        <v>6811760</v>
+        <v>6811582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R38" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649727</v>
+        <v>129649752</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438945</v>
+        <v>439063</v>
       </c>
       <c r="R39" t="n">
-        <v>6811803</v>
+        <v>6811611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649752</v>
+        <v>129649742</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439063</v>
+        <v>439038</v>
       </c>
       <c r="R40" t="n">
-        <v>6811611</v>
+        <v>6811696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649742</v>
+        <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439038</v>
+        <v>439072</v>
       </c>
       <c r="R41" t="n">
-        <v>6811696</v>
+        <v>6811592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,53 +5486,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649685</v>
+        <v>129649697</v>
       </c>
       <c r="B51" t="n">
-        <v>56929</v>
+        <v>78838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439104</v>
+        <v>438961</v>
       </c>
       <c r="R51" t="n">
-        <v>6811591</v>
+        <v>6811763</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5591,10 +5583,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649697</v>
+        <v>129649728</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5602,21 +5594,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5626,10 +5618,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438961</v>
+        <v>438994</v>
       </c>
       <c r="R52" t="n">
-        <v>6811763</v>
+        <v>6811747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5688,45 +5680,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649728</v>
+        <v>129649685</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438994</v>
+        <v>439104</v>
       </c>
       <c r="R53" t="n">
-        <v>6811747</v>
+        <v>6811591</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649687</v>
+        <v>129649696</v>
       </c>
       <c r="B66" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649696</v>
+        <v>129649750</v>
       </c>
       <c r="B67" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R67" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649750</v>
+        <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R68" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,41 +8950,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R86" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9025,7 +9018,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9044,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660890</v>
+        <v>129660836</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,21 +9047,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9079,10 +9071,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438796</v>
+        <v>438795</v>
       </c>
       <c r="R87" t="n">
-        <v>6811854</v>
+        <v>6811868</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9141,10 +9133,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660836</v>
+        <v>129660844</v>
       </c>
       <c r="B88" t="n">
-        <v>79671</v>
+        <v>91620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,34 +9144,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438795</v>
+        <v>438831</v>
       </c>
       <c r="R88" t="n">
-        <v>6811868</v>
+        <v>6811826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9220,6 +9219,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649665</v>
+        <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438999</v>
+        <v>439101</v>
       </c>
       <c r="R3" t="n">
-        <v>6811646</v>
+        <v>6811602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R4" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R5" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649730</v>
+        <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439044</v>
+        <v>438937</v>
       </c>
       <c r="R6" t="n">
-        <v>6811698</v>
+        <v>6811799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649671</v>
+        <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5893,21 +5893,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439129</v>
+        <v>439170</v>
       </c>
       <c r="R55" t="n">
-        <v>6811570</v>
+        <v>6811661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>78838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R56" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6050,11 +6050,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6081,7 +6076,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649737</v>
+        <v>129649732</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439170</v>
+        <v>439106</v>
       </c>
       <c r="R57" t="n">
-        <v>6811661</v>
+        <v>6811690</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6178,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6189,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R58" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6275,10 +6270,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649732</v>
+        <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6286,21 +6281,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439106</v>
+        <v>439132</v>
       </c>
       <c r="R59" t="n">
-        <v>6811690</v>
+        <v>6811591</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6346,6 +6341,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,34 +8950,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R86" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9018,6 +9025,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9036,10 +9044,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660836</v>
+        <v>129660890</v>
       </c>
       <c r="B87" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9047,21 +9055,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9071,10 +9079,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438795</v>
+        <v>438796</v>
       </c>
       <c r="R87" t="n">
-        <v>6811868</v>
+        <v>6811854</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9133,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660844</v>
+        <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>91620</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9144,41 +9152,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438831</v>
+        <v>438795</v>
       </c>
       <c r="R88" t="n">
-        <v>6811826</v>
+        <v>6811868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9219,7 +9220,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R3" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649730</v>
+        <v>129649690</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439044</v>
+        <v>438937</v>
       </c>
       <c r="R4" t="n">
-        <v>6811698</v>
+        <v>6811799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649665</v>
+        <v>129649751</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438999</v>
+        <v>439101</v>
       </c>
       <c r="R5" t="n">
-        <v>6811646</v>
+        <v>6811602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649730</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>439044</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,41 +8950,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R86" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9025,7 +9018,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9044,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660890</v>
+        <v>129660836</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,21 +9047,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9079,10 +9071,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438796</v>
+        <v>438795</v>
       </c>
       <c r="R87" t="n">
-        <v>6811854</v>
+        <v>6811868</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9141,10 +9133,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660836</v>
+        <v>129660844</v>
       </c>
       <c r="B88" t="n">
-        <v>79671</v>
+        <v>91620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,34 +9144,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438795</v>
+        <v>438831</v>
       </c>
       <c r="R88" t="n">
-        <v>6811868</v>
+        <v>6811826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9220,6 +9219,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649665</v>
+        <v>129649730</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438999</v>
+        <v>439044</v>
       </c>
       <c r="R3" t="n">
-        <v>6811646</v>
+        <v>6811698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649690</v>
+        <v>129649665</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438937</v>
+        <v>438999</v>
       </c>
       <c r="R4" t="n">
-        <v>6811799</v>
+        <v>6811646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649730</v>
+        <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439044</v>
+        <v>438937</v>
       </c>
       <c r="R6" t="n">
-        <v>6811698</v>
+        <v>6811799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649729</v>
+        <v>129649734</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439018</v>
+        <v>439124</v>
       </c>
       <c r="R8" t="n">
-        <v>6811719</v>
+        <v>6811683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649734</v>
+        <v>129649729</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439124</v>
+        <v>439018</v>
       </c>
       <c r="R9" t="n">
-        <v>6811683</v>
+        <v>6811719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649700</v>
+        <v>129649699</v>
       </c>
       <c r="B11" t="n">
         <v>78838</v>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438940</v>
+        <v>438935</v>
       </c>
       <c r="R11" t="n">
-        <v>6811804</v>
+        <v>6811797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649699</v>
+        <v>129649700</v>
       </c>
       <c r="B12" t="n">
         <v>78838</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438935</v>
+        <v>438940</v>
       </c>
       <c r="R12" t="n">
-        <v>6811797</v>
+        <v>6811804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129649701</v>
+        <v>129649704</v>
       </c>
       <c r="B20" t="n">
         <v>78838</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439071</v>
+        <v>439142</v>
       </c>
       <c r="R20" t="n">
-        <v>6811718</v>
+        <v>6811627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649704</v>
+        <v>129649701</v>
       </c>
       <c r="B21" t="n">
         <v>78838</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439142</v>
+        <v>439071</v>
       </c>
       <c r="R21" t="n">
-        <v>6811627</v>
+        <v>6811718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R23" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649663</v>
+        <v>129649746</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439158</v>
+        <v>439029</v>
       </c>
       <c r="R26" t="n">
-        <v>6811692</v>
+        <v>6811655</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649746</v>
+        <v>129649663</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439029</v>
+        <v>439158</v>
       </c>
       <c r="R28" t="n">
-        <v>6811655</v>
+        <v>6811692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649743</v>
+        <v>129649731</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438992</v>
+        <v>439095</v>
       </c>
       <c r="R30" t="n">
-        <v>6811688</v>
+        <v>6811729</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129649731</v>
+        <v>129649743</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439095</v>
+        <v>438992</v>
       </c>
       <c r="R31" t="n">
-        <v>6811729</v>
+        <v>6811688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R32" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R33" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649688</v>
+        <v>129649705</v>
       </c>
       <c r="B34" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438959</v>
+        <v>439072</v>
       </c>
       <c r="R34" t="n">
-        <v>6811760</v>
+        <v>6811591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649705</v>
+        <v>129649666</v>
       </c>
       <c r="B35" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439072</v>
+        <v>439131</v>
       </c>
       <c r="R35" t="n">
-        <v>6811591</v>
+        <v>6811582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R37" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R38" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649752</v>
+        <v>129649742</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439063</v>
+        <v>439038</v>
       </c>
       <c r="R39" t="n">
-        <v>6811611</v>
+        <v>6811696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649742</v>
+        <v>129649752</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439038</v>
+        <v>439063</v>
       </c>
       <c r="R40" t="n">
-        <v>6811696</v>
+        <v>6811611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649733</v>
+        <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439097</v>
+        <v>439053</v>
       </c>
       <c r="R42" t="n">
-        <v>6811705</v>
+        <v>6811673</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4679,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4802,7 +4807,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649747</v>
+        <v>129649725</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -4837,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439069</v>
+        <v>438962</v>
       </c>
       <c r="R44" t="n">
-        <v>6811626</v>
+        <v>6811761</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649702</v>
+        <v>129649747</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4910,21 +4915,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439157</v>
+        <v>439069</v>
       </c>
       <c r="R45" t="n">
-        <v>6811682</v>
+        <v>6811626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5093,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649725</v>
+        <v>129649702</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5104,21 +5109,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438962</v>
+        <v>439157</v>
       </c>
       <c r="R47" t="n">
-        <v>6811761</v>
+        <v>6811682</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5190,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649677</v>
+        <v>129649733</v>
       </c>
       <c r="B48" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5201,21 +5206,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5225,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439053</v>
+        <v>439097</v>
       </c>
       <c r="R48" t="n">
-        <v>6811673</v>
+        <v>6811705</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5261,11 +5266,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5486,45 +5486,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649697</v>
+        <v>129649685</v>
       </c>
       <c r="B51" t="n">
-        <v>78838</v>
+        <v>56929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438961</v>
+        <v>439104</v>
       </c>
       <c r="R51" t="n">
-        <v>6811763</v>
+        <v>6811591</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5583,10 +5591,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649728</v>
+        <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5594,21 +5602,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5618,10 +5626,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438994</v>
+        <v>438961</v>
       </c>
       <c r="R52" t="n">
-        <v>6811747</v>
+        <v>6811763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5680,53 +5688,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649685</v>
+        <v>129649728</v>
       </c>
       <c r="B53" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>439104</v>
+        <v>438994</v>
       </c>
       <c r="R53" t="n">
-        <v>6811591</v>
+        <v>6811747</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649737</v>
+        <v>129649732</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439170</v>
+        <v>439106</v>
       </c>
       <c r="R55" t="n">
-        <v>6811661</v>
+        <v>6811690</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649703</v>
+        <v>129649737</v>
       </c>
       <c r="B56" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439167</v>
+        <v>439170</v>
       </c>
       <c r="R56" t="n">
-        <v>6811669</v>
+        <v>6811661</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649732</v>
+        <v>129649703</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439106</v>
+        <v>439167</v>
       </c>
       <c r="R57" t="n">
-        <v>6811690</v>
+        <v>6811669</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649664</v>
+        <v>129649739</v>
       </c>
       <c r="B60" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439138</v>
+        <v>439148</v>
       </c>
       <c r="R60" t="n">
-        <v>6811625</v>
+        <v>6811637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649739</v>
+        <v>129649664</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439148</v>
+        <v>439138</v>
       </c>
       <c r="R62" t="n">
-        <v>6811637</v>
+        <v>6811625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649672</v>
+        <v>129649687</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R65" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649687</v>
+        <v>129649672</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R68" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129660884</v>
+        <v>129660888</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438821</v>
+        <v>438798</v>
       </c>
       <c r="R69" t="n">
-        <v>6811792</v>
+        <v>6811843</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129660888</v>
+        <v>129660884</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438798</v>
+        <v>438821</v>
       </c>
       <c r="R70" t="n">
-        <v>6811843</v>
+        <v>6811792</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,34 +8950,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R86" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9018,6 +9025,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9133,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B88" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9144,41 +9152,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R88" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9219,7 +9220,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649699</v>
+        <v>129649693</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438935</v>
+        <v>439138</v>
       </c>
       <c r="R11" t="n">
-        <v>6811797</v>
+        <v>6811630</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649700</v>
+        <v>129649699</v>
       </c>
       <c r="B12" t="n">
         <v>78838</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438940</v>
+        <v>438935</v>
       </c>
       <c r="R12" t="n">
-        <v>6811804</v>
+        <v>6811797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,53 +1750,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649684</v>
+        <v>129649700</v>
       </c>
       <c r="B13" t="n">
-        <v>56929</v>
+        <v>78838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439120</v>
+        <v>438940</v>
       </c>
       <c r="R13" t="n">
-        <v>6811610</v>
+        <v>6811804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,45 +1847,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649693</v>
+        <v>129649684</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>56929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439138</v>
+        <v>439120</v>
       </c>
       <c r="R14" t="n">
-        <v>6811630</v>
+        <v>6811610</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649661</v>
+        <v>129649692</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439020</v>
+        <v>439167</v>
       </c>
       <c r="R23" t="n">
-        <v>6811728</v>
+        <v>6811669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649692</v>
+        <v>129649741</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439167</v>
+        <v>439100</v>
       </c>
       <c r="R25" t="n">
-        <v>6811669</v>
+        <v>6811652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649694</v>
+        <v>129649742</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439072</v>
+        <v>439038</v>
       </c>
       <c r="R38" t="n">
-        <v>6811592</v>
+        <v>6811696</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649742</v>
+        <v>129649752</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439038</v>
+        <v>439063</v>
       </c>
       <c r="R39" t="n">
-        <v>6811696</v>
+        <v>6811611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649752</v>
+        <v>129649727</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439063</v>
+        <v>438945</v>
       </c>
       <c r="R40" t="n">
-        <v>6811611</v>
+        <v>6811803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R41" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649687</v>
+        <v>129649696</v>
       </c>
       <c r="B65" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649696</v>
+        <v>129649750</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R66" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649750</v>
+        <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>439104</v>
+        <v>438973</v>
       </c>
       <c r="R67" t="n">
-        <v>6811588</v>
+        <v>6811633</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649672</v>
+        <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R68" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8737,10 +8737,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129660886</v>
+        <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8748,34 +8748,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438778</v>
+        <v>438807</v>
       </c>
       <c r="R84" t="n">
-        <v>6811809</v>
+        <v>6811826</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8834,10 +8842,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129660845</v>
+        <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8845,42 +8853,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438807</v>
+        <v>438778</v>
       </c>
       <c r="R85" t="n">
-        <v>6811826</v>
+        <v>6811809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649692</v>
+        <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439167</v>
+        <v>439020</v>
       </c>
       <c r="R23" t="n">
-        <v>6811669</v>
+        <v>6811728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R25" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649742</v>
+        <v>129649694</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439038</v>
+        <v>439072</v>
       </c>
       <c r="R38" t="n">
-        <v>6811696</v>
+        <v>6811592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649752</v>
+        <v>129649742</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439063</v>
+        <v>439038</v>
       </c>
       <c r="R39" t="n">
-        <v>6811611</v>
+        <v>6811696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649727</v>
+        <v>129649752</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438945</v>
+        <v>439063</v>
       </c>
       <c r="R40" t="n">
-        <v>6811803</v>
+        <v>6811611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R73" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B75" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R75" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129649680</v>
       </c>
       <c r="B2" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649730</v>
+        <v>129649751</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439044</v>
+        <v>439101</v>
       </c>
       <c r="R3" t="n">
-        <v>6811698</v>
+        <v>6811602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649665</v>
+        <v>129649730</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438999</v>
+        <v>439044</v>
       </c>
       <c r="R4" t="n">
-        <v>6811646</v>
+        <v>6811698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649751</v>
+        <v>129649665</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439101</v>
+        <v>438999</v>
       </c>
       <c r="R5" t="n">
-        <v>6811602</v>
+        <v>6811646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>129649690</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649734</v>
+        <v>129649729</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439124</v>
+        <v>439018</v>
       </c>
       <c r="R8" t="n">
-        <v>6811683</v>
+        <v>6811719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649729</v>
+        <v>129649734</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439018</v>
+        <v>439124</v>
       </c>
       <c r="R9" t="n">
-        <v>6811719</v>
+        <v>6811683</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>129649749</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649693</v>
+        <v>129649699</v>
       </c>
       <c r="B11" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439138</v>
+        <v>438935</v>
       </c>
       <c r="R11" t="n">
-        <v>6811630</v>
+        <v>6811797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649699</v>
+        <v>129649700</v>
       </c>
       <c r="B12" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438935</v>
+        <v>438940</v>
       </c>
       <c r="R12" t="n">
-        <v>6811797</v>
+        <v>6811804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,45 +1750,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129649700</v>
+        <v>129649684</v>
       </c>
       <c r="B13" t="n">
-        <v>78838</v>
+        <v>56930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438940</v>
+        <v>439120</v>
       </c>
       <c r="R13" t="n">
-        <v>6811804</v>
+        <v>6811610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,53 +1855,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129649684</v>
+        <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>56929</v>
+        <v>78842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439120</v>
+        <v>439138</v>
       </c>
       <c r="R14" t="n">
-        <v>6811610</v>
+        <v>6811630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129649682</v>
+        <v>129649683</v>
       </c>
       <c r="B16" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439062</v>
+        <v>439106</v>
       </c>
       <c r="R16" t="n">
         <v>6811611</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649683</v>
+        <v>129649682</v>
       </c>
       <c r="B17" t="n">
-        <v>56929</v>
+        <v>56930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439106</v>
+        <v>439062</v>
       </c>
       <c r="R17" t="n">
         <v>6811611</v>
@@ -2259,53 +2259,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649681</v>
+        <v>129649744</v>
       </c>
       <c r="B18" t="n">
-        <v>56929</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439028</v>
+        <v>438987</v>
       </c>
       <c r="R18" t="n">
-        <v>6811657</v>
+        <v>6811668</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,11 +2330,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,7 +2359,7 @@
         <v>129649667</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2456,7 @@
         <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2553,7 @@
         <v>129649701</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,45 +2647,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649744</v>
+        <v>129649681</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>56930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438987</v>
+        <v>439028</v>
       </c>
       <c r="R22" t="n">
-        <v>6811668</v>
+        <v>6811657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R23" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649746</v>
+        <v>129649663</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439029</v>
+        <v>439158</v>
       </c>
       <c r="R26" t="n">
-        <v>6811655</v>
+        <v>6811692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,45 +3145,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649756</v>
+        <v>129649679</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>56930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438993</v>
+        <v>439074</v>
       </c>
       <c r="R27" t="n">
-        <v>6811613</v>
+        <v>6811666</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649663</v>
+        <v>129649756</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3261,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3285,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439158</v>
+        <v>438993</v>
       </c>
       <c r="R28" t="n">
-        <v>6811692</v>
+        <v>6811613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,53 +3347,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649679</v>
+        <v>129649746</v>
       </c>
       <c r="B29" t="n">
-        <v>56929</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439074</v>
+        <v>439029</v>
       </c>
       <c r="R29" t="n">
-        <v>6811666</v>
+        <v>6811655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3444,10 +3444,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129649731</v>
+        <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439095</v>
+        <v>438992</v>
       </c>
       <c r="R30" t="n">
-        <v>6811729</v>
+        <v>6811688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129649743</v>
+        <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438992</v>
+        <v>439095</v>
       </c>
       <c r="R31" t="n">
-        <v>6811688</v>
+        <v>6811729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R32" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R33" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649705</v>
+        <v>129649688</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439072</v>
+        <v>438959</v>
       </c>
       <c r="R34" t="n">
-        <v>6811591</v>
+        <v>6811760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649666</v>
+        <v>129649740</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439131</v>
+        <v>439121</v>
       </c>
       <c r="R35" t="n">
-        <v>6811582</v>
+        <v>6811628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649740</v>
+        <v>129649705</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439121</v>
+        <v>439072</v>
       </c>
       <c r="R36" t="n">
-        <v>6811628</v>
+        <v>6811591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649688</v>
+        <v>129649666</v>
       </c>
       <c r="B37" t="n">
-        <v>78839</v>
+        <v>79703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438959</v>
+        <v>439131</v>
       </c>
       <c r="R37" t="n">
-        <v>6811760</v>
+        <v>6811582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649694</v>
+        <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439072</v>
+        <v>438945</v>
       </c>
       <c r="R38" t="n">
-        <v>6811592</v>
+        <v>6811803</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649742</v>
+        <v>129649752</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439038</v>
+        <v>439063</v>
       </c>
       <c r="R39" t="n">
-        <v>6811696</v>
+        <v>6811611</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649752</v>
+        <v>129649742</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439063</v>
+        <v>439038</v>
       </c>
       <c r="R40" t="n">
-        <v>6811611</v>
+        <v>6811696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649727</v>
+        <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438945</v>
+        <v>439072</v>
       </c>
       <c r="R41" t="n">
-        <v>6811803</v>
+        <v>6811592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649677</v>
+        <v>129649702</v>
       </c>
       <c r="B42" t="n">
-        <v>91620</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439053</v>
+        <v>439157</v>
       </c>
       <c r="R42" t="n">
-        <v>6811673</v>
+        <v>6811682</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4710,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649738</v>
+        <v>129649677</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439156</v>
+        <v>439053</v>
       </c>
       <c r="R43" t="n">
-        <v>6811648</v>
+        <v>6811673</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4781,6 +4776,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649725</v>
+        <v>129649733</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438962</v>
+        <v>439097</v>
       </c>
       <c r="R44" t="n">
-        <v>6811761</v>
+        <v>6811705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649747</v>
+        <v>129649738</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439069</v>
+        <v>439156</v>
       </c>
       <c r="R45" t="n">
-        <v>6811626</v>
+        <v>6811648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649736</v>
+        <v>129649747</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439165</v>
+        <v>439069</v>
       </c>
       <c r="R46" t="n">
-        <v>6811686</v>
+        <v>6811626</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649702</v>
+        <v>129649736</v>
       </c>
       <c r="B47" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439157</v>
+        <v>439165</v>
       </c>
       <c r="R47" t="n">
-        <v>6811682</v>
+        <v>6811686</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649733</v>
+        <v>129649725</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439097</v>
+        <v>438962</v>
       </c>
       <c r="R48" t="n">
-        <v>6811705</v>
+        <v>6811761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5486,53 +5486,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129649685</v>
+        <v>129649728</v>
       </c>
       <c r="B51" t="n">
-        <v>56929</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439104</v>
+        <v>438994</v>
       </c>
       <c r="R51" t="n">
-        <v>6811591</v>
+        <v>6811747</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5594,7 +5586,7 @@
         <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5688,45 +5680,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649728</v>
+        <v>129649685</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>56930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438994</v>
+        <v>439104</v>
       </c>
       <c r="R53" t="n">
-        <v>6811747</v>
+        <v>6811591</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129649732</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649737</v>
+        <v>129649671</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439170</v>
+        <v>439129</v>
       </c>
       <c r="R56" t="n">
-        <v>6811661</v>
+        <v>6811570</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649703</v>
+        <v>129649675</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>57895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439167</v>
+        <v>439132</v>
       </c>
       <c r="R57" t="n">
-        <v>6811669</v>
+        <v>6811591</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6147,6 +6147,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6173,10 +6178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649737</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6189,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439170</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811661</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6270,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B59" t="n">
-        <v>57896</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R59" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6341,11 +6346,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R60" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649754</v>
+        <v>129649739</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439022</v>
+        <v>439148</v>
       </c>
       <c r="R61" t="n">
-        <v>6811624</v>
+        <v>6811637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
         <v>129649664</v>
       </c>
       <c r="B62" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>129649691</v>
       </c>
       <c r="B63" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129649676</v>
       </c>
       <c r="B64" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649696</v>
+        <v>129649750</v>
       </c>
       <c r="B65" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R65" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649750</v>
+        <v>129649696</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R66" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7067,7 +7067,7 @@
         <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7258,10 +7258,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129660888</v>
+        <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438798</v>
+        <v>438821</v>
       </c>
       <c r="R69" t="n">
-        <v>6811843</v>
+        <v>6811792</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129660884</v>
+        <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438821</v>
+        <v>438798</v>
       </c>
       <c r="R70" t="n">
-        <v>6811792</v>
+        <v>6811843</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B73" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7746,7 +7746,7 @@
         <v>129660856</v>
       </c>
       <c r="B74" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R75" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660855</v>
+        <v>129660835</v>
       </c>
       <c r="B79" t="n">
-        <v>78838</v>
+        <v>79674</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438795</v>
+        <v>438807</v>
       </c>
       <c r="R79" t="n">
-        <v>6811815</v>
+        <v>6811845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,10 +8325,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B80" t="n">
-        <v>79671</v>
+        <v>78841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8336,21 +8336,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R80" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8422,32 +8422,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660839</v>
+        <v>129660841</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>56927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8465,10 +8465,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438773</v>
+        <v>438785</v>
       </c>
       <c r="R81" t="n">
-        <v>6811783</v>
+        <v>6811874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8527,32 +8527,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B82" t="n">
-        <v>56926</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R82" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
         <v>129660842</v>
       </c>
       <c r="B83" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>129660844</v>
       </c>
       <c r="B86" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660836</v>
+        <v>129660890</v>
       </c>
       <c r="B87" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,21 +9055,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438795</v>
+        <v>438796</v>
       </c>
       <c r="R87" t="n">
-        <v>6811868</v>
+        <v>6811854</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9141,10 +9141,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660890</v>
+        <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,21 +9152,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438796</v>
+        <v>438795</v>
       </c>
       <c r="R88" t="n">
-        <v>6811854</v>
+        <v>6811868</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129649751</v>
+        <v>129649690</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439101</v>
+        <v>438937</v>
       </c>
       <c r="R3" t="n">
-        <v>6811602</v>
+        <v>6811799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129649730</v>
+        <v>129649751</v>
       </c>
       <c r="B4" t="n">
         <v>79084</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439044</v>
+        <v>439101</v>
       </c>
       <c r="R4" t="n">
-        <v>6811698</v>
+        <v>6811602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129649665</v>
+        <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438999</v>
+        <v>439044</v>
       </c>
       <c r="R5" t="n">
-        <v>6811646</v>
+        <v>6811698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129649690</v>
+        <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438937</v>
+        <v>438999</v>
       </c>
       <c r="R6" t="n">
-        <v>6811799</v>
+        <v>6811646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649729</v>
+        <v>129649749</v>
       </c>
       <c r="B8" t="n">
         <v>79084</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439018</v>
+        <v>439112</v>
       </c>
       <c r="R8" t="n">
-        <v>6811719</v>
+        <v>6811610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649734</v>
+        <v>129649729</v>
       </c>
       <c r="B9" t="n">
         <v>79084</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439124</v>
+        <v>439018</v>
       </c>
       <c r="R9" t="n">
-        <v>6811683</v>
+        <v>6811719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129649749</v>
+        <v>129649734</v>
       </c>
       <c r="B10" t="n">
         <v>79084</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439112</v>
+        <v>439124</v>
       </c>
       <c r="R10" t="n">
-        <v>6811610</v>
+        <v>6811683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649692</v>
       </c>
       <c r="B24" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439167</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811669</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649692</v>
+        <v>129649661</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439167</v>
+        <v>439020</v>
       </c>
       <c r="R25" t="n">
-        <v>6811669</v>
+        <v>6811728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649663</v>
+        <v>129649756</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439158</v>
+        <v>438993</v>
       </c>
       <c r="R26" t="n">
-        <v>6811692</v>
+        <v>6811613</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,53 +3145,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649679</v>
+        <v>129649746</v>
       </c>
       <c r="B27" t="n">
-        <v>56930</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439074</v>
+        <v>439029</v>
       </c>
       <c r="R27" t="n">
-        <v>6811666</v>
+        <v>6811655</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649756</v>
+        <v>129649663</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3261,21 +3253,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3285,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438993</v>
+        <v>439158</v>
       </c>
       <c r="R28" t="n">
-        <v>6811613</v>
+        <v>6811692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,45 +3339,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649746</v>
+        <v>129649679</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>56930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439029</v>
+        <v>439074</v>
       </c>
       <c r="R29" t="n">
-        <v>6811655</v>
+        <v>6811666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129649732</v>
+        <v>129649737</v>
       </c>
       <c r="B55" t="n">
         <v>79084</v>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439106</v>
+        <v>439170</v>
       </c>
       <c r="R55" t="n">
-        <v>6811690</v>
+        <v>6811661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129649671</v>
+        <v>129649732</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439129</v>
+        <v>439106</v>
       </c>
       <c r="R56" t="n">
-        <v>6811570</v>
+        <v>6811690</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B57" t="n">
-        <v>57895</v>
+        <v>78841</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R57" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6147,11 +6147,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6178,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649737</v>
+        <v>129649671</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6189,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6213,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439170</v>
+        <v>439129</v>
       </c>
       <c r="R58" t="n">
-        <v>6811661</v>
+        <v>6811570</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6275,10 +6270,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649703</v>
+        <v>129649675</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>57895</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6286,21 +6281,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439167</v>
+        <v>439132</v>
       </c>
       <c r="R59" t="n">
-        <v>6811669</v>
+        <v>6811591</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6346,6 +6341,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649754</v>
+        <v>129649691</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439022</v>
+        <v>439156</v>
       </c>
       <c r="R60" t="n">
-        <v>6811624</v>
+        <v>6811687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B61" t="n">
         <v>79084</v>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R61" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649664</v>
+        <v>129649739</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439138</v>
+        <v>439148</v>
       </c>
       <c r="R62" t="n">
-        <v>6811625</v>
+        <v>6811637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649691</v>
+        <v>129649664</v>
       </c>
       <c r="B63" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439156</v>
+        <v>439138</v>
       </c>
       <c r="R63" t="n">
-        <v>6811687</v>
+        <v>6811625</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649750</v>
+        <v>129649687</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R65" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649672</v>
+        <v>129649750</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438973</v>
+        <v>439104</v>
       </c>
       <c r="R67" t="n">
-        <v>6811633</v>
+        <v>6811588</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649687</v>
+        <v>129649672</v>
       </c>
       <c r="B68" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R68" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8228,10 +8228,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B79" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8239,21 +8239,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R79" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,45 +8325,53 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660855</v>
+        <v>129660841</v>
       </c>
       <c r="B80" t="n">
-        <v>78841</v>
+        <v>56927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438795</v>
+        <v>438785</v>
       </c>
       <c r="R80" t="n">
-        <v>6811815</v>
+        <v>6811874</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8422,32 +8430,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B81" t="n">
-        <v>56927</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8455,7 +8463,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8465,10 +8473,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R81" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8527,10 +8535,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660839</v>
+        <v>129660835</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>79674</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8538,42 +8546,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438773</v>
+        <v>438807</v>
       </c>
       <c r="R82" t="n">
-        <v>6811783</v>
+        <v>6811845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129649680</v>
       </c>
       <c r="B2" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129649690</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129649751</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649749</v>
+        <v>129649729</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439112</v>
+        <v>439018</v>
       </c>
       <c r="R8" t="n">
-        <v>6811610</v>
+        <v>6811719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649729</v>
+        <v>129649749</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439018</v>
+        <v>439112</v>
       </c>
       <c r="R9" t="n">
-        <v>6811719</v>
+        <v>6811610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>129649734</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129649699</v>
+        <v>129649700</v>
       </c>
       <c r="B11" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438935</v>
+        <v>438940</v>
       </c>
       <c r="R11" t="n">
-        <v>6811797</v>
+        <v>6811804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129649700</v>
+        <v>129649699</v>
       </c>
       <c r="B12" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438940</v>
+        <v>438935</v>
       </c>
       <c r="R12" t="n">
-        <v>6811804</v>
+        <v>6811797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>129649684</v>
       </c>
       <c r="B13" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129649735</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129649683</v>
+        <v>129649682</v>
       </c>
       <c r="B16" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439106</v>
+        <v>439062</v>
       </c>
       <c r="R16" t="n">
         <v>6811611</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649682</v>
+        <v>129649683</v>
       </c>
       <c r="B17" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439062</v>
+        <v>439106</v>
       </c>
       <c r="R17" t="n">
         <v>6811611</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129649744</v>
+        <v>129649667</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438987</v>
+        <v>439072</v>
       </c>
       <c r="R18" t="n">
-        <v>6811668</v>
+        <v>6811592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129649667</v>
+        <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2367,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439072</v>
+        <v>439071</v>
       </c>
       <c r="R19" t="n">
-        <v>6811592</v>
+        <v>6811718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
         <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2550,45 +2550,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649701</v>
+        <v>129649681</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>56933</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439071</v>
+        <v>439028</v>
       </c>
       <c r="R21" t="n">
-        <v>6811718</v>
+        <v>6811657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,6 +2629,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2647,53 +2660,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649681</v>
+        <v>129649744</v>
       </c>
       <c r="B22" t="n">
-        <v>56930</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439028</v>
+        <v>438987</v>
       </c>
       <c r="R22" t="n">
-        <v>6811657</v>
+        <v>6811668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,11 +2731,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2760,7 +2760,7 @@
         <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649692</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439167</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811669</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649661</v>
+        <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439020</v>
+        <v>439167</v>
       </c>
       <c r="R25" t="n">
-        <v>6811728</v>
+        <v>6811669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3048,45 +3048,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129649756</v>
+        <v>129649679</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>56933</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438993</v>
+        <v>439074</v>
       </c>
       <c r="R26" t="n">
-        <v>6811613</v>
+        <v>6811666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,10 +3153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649746</v>
+        <v>129649756</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3180,10 +3188,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439029</v>
+        <v>438993</v>
       </c>
       <c r="R27" t="n">
-        <v>6811655</v>
+        <v>6811613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649663</v>
+        <v>129649746</v>
       </c>
       <c r="B28" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,21 +3261,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3277,10 +3285,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439158</v>
+        <v>439029</v>
       </c>
       <c r="R28" t="n">
-        <v>6811692</v>
+        <v>6811655</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,53 +3347,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649679</v>
+        <v>129649663</v>
       </c>
       <c r="B29" t="n">
-        <v>56930</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439074</v>
+        <v>439158</v>
       </c>
       <c r="R29" t="n">
-        <v>6811666</v>
+        <v>6811692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>129649755</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>129649662</v>
       </c>
       <c r="B33" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649688</v>
+        <v>129649705</v>
       </c>
       <c r="B34" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438959</v>
+        <v>439072</v>
       </c>
       <c r="R34" t="n">
-        <v>6811760</v>
+        <v>6811591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649740</v>
+        <v>129649666</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439121</v>
+        <v>439131</v>
       </c>
       <c r="R35" t="n">
-        <v>6811628</v>
+        <v>6811582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649705</v>
+        <v>129649740</v>
       </c>
       <c r="B36" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439072</v>
+        <v>439121</v>
       </c>
       <c r="R36" t="n">
-        <v>6811591</v>
+        <v>6811628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129649666</v>
+        <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439131</v>
+        <v>438959</v>
       </c>
       <c r="R37" t="n">
-        <v>6811582</v>
+        <v>6811760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4223,7 +4223,7 @@
         <v>129649727</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>129649752</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>129649742</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>129649694</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649702</v>
+        <v>129649677</v>
       </c>
       <c r="B42" t="n">
-        <v>78841</v>
+        <v>91626</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439157</v>
+        <v>439053</v>
       </c>
       <c r="R42" t="n">
-        <v>6811682</v>
+        <v>6811673</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,6 +4679,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4705,10 +4710,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649677</v>
+        <v>129649733</v>
       </c>
       <c r="B43" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4721,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439053</v>
+        <v>439097</v>
       </c>
       <c r="R43" t="n">
-        <v>6811673</v>
+        <v>6811705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4776,11 +4781,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649733</v>
+        <v>129649738</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439097</v>
+        <v>439156</v>
       </c>
       <c r="R44" t="n">
-        <v>6811705</v>
+        <v>6811648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649738</v>
+        <v>129649747</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439156</v>
+        <v>439069</v>
       </c>
       <c r="R45" t="n">
-        <v>6811648</v>
+        <v>6811626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649747</v>
+        <v>129649736</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439069</v>
+        <v>439165</v>
       </c>
       <c r="R46" t="n">
-        <v>6811626</v>
+        <v>6811686</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649736</v>
+        <v>129649725</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439165</v>
+        <v>438962</v>
       </c>
       <c r="R47" t="n">
-        <v>6811686</v>
+        <v>6811761</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649725</v>
+        <v>129649702</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438962</v>
+        <v>439157</v>
       </c>
       <c r="R48" t="n">
-        <v>6811761</v>
+        <v>6811682</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>129649728</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>129649697</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>129649685</v>
       </c>
       <c r="B53" t="n">
-        <v>56930</v>
+        <v>56933</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129649732</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B57" t="n">
-        <v>78841</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R57" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649671</v>
+        <v>129649675</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439129</v>
+        <v>439132</v>
       </c>
       <c r="R58" t="n">
-        <v>6811570</v>
+        <v>6811591</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6244,6 +6244,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6270,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B59" t="n">
-        <v>57895</v>
+        <v>78844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6281,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R59" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6341,11 +6346,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649691</v>
+        <v>129649754</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439156</v>
+        <v>439022</v>
       </c>
       <c r="R60" t="n">
-        <v>6811687</v>
+        <v>6811624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649754</v>
+        <v>129649739</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439022</v>
+        <v>439148</v>
       </c>
       <c r="R61" t="n">
-        <v>6811624</v>
+        <v>6811637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649739</v>
+        <v>129649691</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439148</v>
+        <v>439156</v>
       </c>
       <c r="R62" t="n">
-        <v>6811637</v>
+        <v>6811687</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6666,7 +6666,7 @@
         <v>129649664</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>129649676</v>
       </c>
       <c r="B64" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649687</v>
+        <v>129649750</v>
       </c>
       <c r="B65" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438968</v>
+        <v>439104</v>
       </c>
       <c r="R65" t="n">
-        <v>6811757</v>
+        <v>6811588</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6970,7 +6970,7 @@
         <v>129649696</v>
       </c>
       <c r="B66" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649750</v>
+        <v>129649672</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>439104</v>
+        <v>438973</v>
       </c>
       <c r="R67" t="n">
-        <v>6811588</v>
+        <v>6811633</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649672</v>
+        <v>129649687</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R68" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7261,7 +7261,7 @@
         <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R73" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660856</v>
+        <v>129660885</v>
       </c>
       <c r="B74" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438810</v>
+        <v>438717</v>
       </c>
       <c r="R74" t="n">
-        <v>6811833</v>
+        <v>6811848</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660848</v>
+        <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438790</v>
+        <v>438810</v>
       </c>
       <c r="R75" t="n">
-        <v>6811814</v>
+        <v>6811833</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,45 +8228,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660855</v>
+        <v>129660841</v>
       </c>
       <c r="B79" t="n">
-        <v>78841</v>
+        <v>56930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438795</v>
+        <v>438785</v>
       </c>
       <c r="R79" t="n">
-        <v>6811815</v>
+        <v>6811874</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8325,53 +8333,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660841</v>
+        <v>129660835</v>
       </c>
       <c r="B80" t="n">
-        <v>56927</v>
+        <v>79677</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438785</v>
+        <v>438807</v>
       </c>
       <c r="R80" t="n">
-        <v>6811874</v>
+        <v>6811845</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,10 +8430,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660839</v>
+        <v>129660855</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8441,42 +8441,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438773</v>
+        <v>438795</v>
       </c>
       <c r="R81" t="n">
-        <v>6811783</v>
+        <v>6811815</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8535,10 +8527,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660835</v>
+        <v>129660839</v>
       </c>
       <c r="B82" t="n">
-        <v>79674</v>
+        <v>57740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8546,34 +8538,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438807</v>
+        <v>438773</v>
       </c>
       <c r="R82" t="n">
-        <v>6811845</v>
+        <v>6811783</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8635,7 +8635,7 @@
         <v>129660842</v>
       </c>
       <c r="B83" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>129660845</v>
       </c>
       <c r="B84" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129660844</v>
+        <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8950,41 +8950,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438831</v>
+        <v>438796</v>
       </c>
       <c r="R86" t="n">
-        <v>6811826</v>
+        <v>6811854</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9025,7 +9018,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9044,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660890</v>
+        <v>129660844</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9055,34 +9047,41 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438796</v>
+        <v>438831</v>
       </c>
       <c r="R87" t="n">
-        <v>6811854</v>
+        <v>6811826</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9123,6 +9122,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>129660836</v>
       </c>
       <c r="B88" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649741</v>
+        <v>129649692</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439100</v>
+        <v>439167</v>
       </c>
       <c r="R23" t="n">
-        <v>6811652</v>
+        <v>6811669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649692</v>
+        <v>129649661</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439167</v>
+        <v>439020</v>
       </c>
       <c r="R25" t="n">
-        <v>6811669</v>
+        <v>6811728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B73" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660885</v>
+        <v>129660856</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438717</v>
+        <v>438810</v>
       </c>
       <c r="R74" t="n">
-        <v>6811848</v>
+        <v>6811833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B75" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R75" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8228,32 +8228,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660841</v>
+        <v>129660839</v>
       </c>
       <c r="B79" t="n">
-        <v>56930</v>
+        <v>57740</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8261,7 +8261,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438785</v>
+        <v>438773</v>
       </c>
       <c r="R79" t="n">
-        <v>6811874</v>
+        <v>6811783</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660835</v>
+        <v>129660855</v>
       </c>
       <c r="B80" t="n">
-        <v>79677</v>
+        <v>78844</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8344,21 +8344,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438807</v>
+        <v>438795</v>
       </c>
       <c r="R80" t="n">
-        <v>6811845</v>
+        <v>6811815</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,45 +8430,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660855</v>
+        <v>129660841</v>
       </c>
       <c r="B81" t="n">
-        <v>78844</v>
+        <v>56930</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438795</v>
+        <v>438785</v>
       </c>
       <c r="R81" t="n">
-        <v>6811815</v>
+        <v>6811874</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8527,10 +8535,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129660839</v>
+        <v>129660835</v>
       </c>
       <c r="B82" t="n">
-        <v>57740</v>
+        <v>79677</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8538,42 +8546,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438773</v>
+        <v>438807</v>
       </c>
       <c r="R82" t="n">
-        <v>6811783</v>
+        <v>6811845</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -2550,53 +2550,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129649681</v>
+        <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>56933</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439028</v>
+        <v>438987</v>
       </c>
       <c r="R21" t="n">
-        <v>6811657</v>
+        <v>6811668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2629,11 +2621,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2660,45 +2647,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129649744</v>
+        <v>129649681</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>56933</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438987</v>
+        <v>439028</v>
       </c>
       <c r="R22" t="n">
-        <v>6811668</v>
+        <v>6811657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,6 +2726,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>över 20 individer flög iväg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649692</v>
+        <v>129649741</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439167</v>
+        <v>439100</v>
       </c>
       <c r="R23" t="n">
-        <v>6811669</v>
+        <v>6811652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R24" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129649661</v>
+        <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439020</v>
+        <v>439167</v>
       </c>
       <c r="R25" t="n">
-        <v>6811728</v>
+        <v>6811669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649705</v>
+        <v>129649740</v>
       </c>
       <c r="B34" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439072</v>
+        <v>439121</v>
       </c>
       <c r="R34" t="n">
-        <v>6811591</v>
+        <v>6811628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649666</v>
+        <v>129649705</v>
       </c>
       <c r="B35" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439131</v>
+        <v>439072</v>
       </c>
       <c r="R35" t="n">
-        <v>6811582</v>
+        <v>6811591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649740</v>
+        <v>129649666</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439121</v>
+        <v>439131</v>
       </c>
       <c r="R36" t="n">
-        <v>6811628</v>
+        <v>6811582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649691</v>
+        <v>129649676</v>
       </c>
       <c r="B62" t="n">
-        <v>78845</v>
+        <v>57898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,34 +6577,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>439156</v>
+        <v>438971</v>
       </c>
       <c r="R62" t="n">
-        <v>6811687</v>
+        <v>6811657</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6637,6 +6645,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6663,10 +6676,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649664</v>
+        <v>129649691</v>
       </c>
       <c r="B63" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6674,21 +6687,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6698,10 +6711,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439138</v>
+        <v>439156</v>
       </c>
       <c r="R63" t="n">
-        <v>6811625</v>
+        <v>6811687</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6760,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649676</v>
+        <v>129649664</v>
       </c>
       <c r="B64" t="n">
-        <v>57898</v>
+        <v>79706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6771,42 +6784,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438971</v>
+        <v>439138</v>
       </c>
       <c r="R64" t="n">
-        <v>6811657</v>
+        <v>6811625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6839,11 +6844,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649750</v>
+        <v>129649687</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>439104</v>
+        <v>438968</v>
       </c>
       <c r="R65" t="n">
-        <v>6811588</v>
+        <v>6811757</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649696</v>
+        <v>129649672</v>
       </c>
       <c r="B66" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R66" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7064,10 +7064,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129649672</v>
+        <v>129649750</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438973</v>
+        <v>439104</v>
       </c>
       <c r="R67" t="n">
-        <v>6811633</v>
+        <v>6811588</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649687</v>
+        <v>129649696</v>
       </c>
       <c r="B68" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660885</v>
+        <v>129660848</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438717</v>
+        <v>438790</v>
       </c>
       <c r="R73" t="n">
-        <v>6811848</v>
+        <v>6811814</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660856</v>
+        <v>129660885</v>
       </c>
       <c r="B74" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438810</v>
+        <v>438717</v>
       </c>
       <c r="R74" t="n">
-        <v>6811833</v>
+        <v>6811848</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660848</v>
+        <v>129660856</v>
       </c>
       <c r="B75" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438790</v>
+        <v>438810</v>
       </c>
       <c r="R75" t="n">
-        <v>6811814</v>
+        <v>6811833</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129649690</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129649751</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129649730</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>129649665</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129649669</v>
       </c>
       <c r="B7" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129649729</v>
+        <v>129649734</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439018</v>
+        <v>439124</v>
       </c>
       <c r="R8" t="n">
-        <v>6811719</v>
+        <v>6811683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129649749</v>
+        <v>129649729</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439112</v>
+        <v>439018</v>
       </c>
       <c r="R9" t="n">
-        <v>6811610</v>
+        <v>6811719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129649734</v>
+        <v>129649749</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439124</v>
+        <v>439112</v>
       </c>
       <c r="R10" t="n">
-        <v>6811683</v>
+        <v>6811610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>129649700</v>
       </c>
       <c r="B11" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>129649699</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>129649693</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,45 +1952,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129649735</v>
+        <v>129649682</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>56933</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439148</v>
+        <v>439062</v>
       </c>
       <c r="R15" t="n">
-        <v>6811695</v>
+        <v>6811611</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,7 +2057,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129649682</v>
+        <v>129649683</v>
       </c>
       <c r="B16" t="n">
         <v>56933</v>
@@ -2092,7 +2100,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439062</v>
+        <v>439106</v>
       </c>
       <c r="R16" t="n">
         <v>6811611</v>
@@ -2154,53 +2162,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129649683</v>
+        <v>129649735</v>
       </c>
       <c r="B17" t="n">
-        <v>56933</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439106</v>
+        <v>439148</v>
       </c>
       <c r="R17" t="n">
-        <v>6811611</v>
+        <v>6811695</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
         <v>129649667</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>129649701</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>129649704</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>129649744</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129649741</v>
+        <v>129649661</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,21 +2768,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439100</v>
+        <v>439020</v>
       </c>
       <c r="R23" t="n">
-        <v>6811652</v>
+        <v>6811728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2854,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129649661</v>
+        <v>129649741</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2865,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439020</v>
+        <v>439100</v>
       </c>
       <c r="R24" t="n">
-        <v>6811728</v>
+        <v>6811652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
         <v>129649692</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129649756</v>
+        <v>129649663</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438993</v>
+        <v>439158</v>
       </c>
       <c r="R27" t="n">
-        <v>6811613</v>
+        <v>6811692</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129649746</v>
+        <v>129649756</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439029</v>
+        <v>438993</v>
       </c>
       <c r="R28" t="n">
-        <v>6811655</v>
+        <v>6811613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129649663</v>
+        <v>129649746</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439158</v>
+        <v>439029</v>
       </c>
       <c r="R29" t="n">
-        <v>6811692</v>
+        <v>6811655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,7 +3447,7 @@
         <v>129649743</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>129649731</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129649755</v>
+        <v>129649662</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439002</v>
+        <v>439140</v>
       </c>
       <c r="R32" t="n">
-        <v>6811617</v>
+        <v>6811702</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129649662</v>
+        <v>129649755</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3746,21 +3746,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439140</v>
+        <v>439002</v>
       </c>
       <c r="R33" t="n">
-        <v>6811702</v>
+        <v>6811617</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3832,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129649740</v>
+        <v>129649705</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439121</v>
+        <v>439072</v>
       </c>
       <c r="R34" t="n">
-        <v>6811628</v>
+        <v>6811591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129649705</v>
+        <v>129649666</v>
       </c>
       <c r="B35" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439072</v>
+        <v>439131</v>
       </c>
       <c r="R35" t="n">
-        <v>6811591</v>
+        <v>6811582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129649666</v>
+        <v>129649740</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4037,21 +4037,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439131</v>
+        <v>439121</v>
       </c>
       <c r="R36" t="n">
-        <v>6811582</v>
+        <v>6811628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4126,7 +4126,7 @@
         <v>129649688</v>
       </c>
       <c r="B37" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129649727</v>
+        <v>129649742</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438945</v>
+        <v>439038</v>
       </c>
       <c r="R38" t="n">
-        <v>6811803</v>
+        <v>6811696</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129649752</v>
+        <v>129649694</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4328,21 +4328,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439063</v>
+        <v>439072</v>
       </c>
       <c r="R39" t="n">
-        <v>6811611</v>
+        <v>6811592</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129649742</v>
+        <v>129649727</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439038</v>
+        <v>438945</v>
       </c>
       <c r="R40" t="n">
-        <v>6811696</v>
+        <v>6811803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129649694</v>
+        <v>129649752</v>
       </c>
       <c r="B41" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439072</v>
+        <v>439063</v>
       </c>
       <c r="R41" t="n">
-        <v>6811592</v>
+        <v>6811611</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129649677</v>
+        <v>129649702</v>
       </c>
       <c r="B42" t="n">
-        <v>91626</v>
+        <v>78845</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4619,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439053</v>
+        <v>439157</v>
       </c>
       <c r="R42" t="n">
-        <v>6811673</v>
+        <v>6811682</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4679,11 +4679,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4710,10 +4705,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129649733</v>
+        <v>129649677</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,21 +4716,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439097</v>
+        <v>439053</v>
       </c>
       <c r="R43" t="n">
-        <v>6811705</v>
+        <v>6811673</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4781,6 +4776,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129649738</v>
+        <v>129649733</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439156</v>
+        <v>439097</v>
       </c>
       <c r="R44" t="n">
-        <v>6811648</v>
+        <v>6811705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129649747</v>
+        <v>129649738</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439069</v>
+        <v>439156</v>
       </c>
       <c r="R45" t="n">
-        <v>6811626</v>
+        <v>6811648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129649736</v>
+        <v>129649747</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439165</v>
+        <v>439069</v>
       </c>
       <c r="R46" t="n">
-        <v>6811686</v>
+        <v>6811626</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129649725</v>
+        <v>129649736</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438962</v>
+        <v>439165</v>
       </c>
       <c r="R47" t="n">
-        <v>6811761</v>
+        <v>6811686</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129649702</v>
+        <v>129649725</v>
       </c>
       <c r="B48" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439157</v>
+        <v>438962</v>
       </c>
       <c r="R48" t="n">
-        <v>6811682</v>
+        <v>6811761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>129649753</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>129649745</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>129649728</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5583,45 +5583,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129649697</v>
+        <v>129649685</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>56933</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438961</v>
+        <v>439104</v>
       </c>
       <c r="R52" t="n">
-        <v>6811763</v>
+        <v>6811591</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5680,53 +5688,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129649685</v>
+        <v>129649697</v>
       </c>
       <c r="B53" t="n">
-        <v>56933</v>
+        <v>78845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>439104</v>
+        <v>438961</v>
       </c>
       <c r="R53" t="n">
-        <v>6811591</v>
+        <v>6811763</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5788,7 +5788,7 @@
         <v>129649748</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129649737</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129649732</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129649671</v>
+        <v>129649675</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6087,21 +6087,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439129</v>
+        <v>439132</v>
       </c>
       <c r="R57" t="n">
-        <v>6811570</v>
+        <v>6811591</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6147,6 +6147,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6173,10 +6178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129649675</v>
+        <v>129649703</v>
       </c>
       <c r="B58" t="n">
-        <v>57898</v>
+        <v>78845</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6184,21 +6189,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6208,10 +6213,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439132</v>
+        <v>439167</v>
       </c>
       <c r="R58" t="n">
-        <v>6811591</v>
+        <v>6811669</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6244,11 +6249,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6275,10 +6275,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129649703</v>
+        <v>129649671</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6286,21 +6286,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>439167</v>
+        <v>439129</v>
       </c>
       <c r="R59" t="n">
-        <v>6811669</v>
+        <v>6811570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129649754</v>
+        <v>129649664</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>439022</v>
+        <v>439138</v>
       </c>
       <c r="R60" t="n">
-        <v>6811624</v>
+        <v>6811625</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6469,10 +6469,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129649739</v>
+        <v>129649754</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>439148</v>
+        <v>439022</v>
       </c>
       <c r="R61" t="n">
-        <v>6811637</v>
+        <v>6811624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6566,10 +6566,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129649676</v>
+        <v>129649739</v>
       </c>
       <c r="B62" t="n">
-        <v>57898</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6577,42 +6577,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438971</v>
+        <v>439148</v>
       </c>
       <c r="R62" t="n">
-        <v>6811657</v>
+        <v>6811637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6645,11 +6637,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6676,10 +6663,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129649691</v>
+        <v>129649676</v>
       </c>
       <c r="B63" t="n">
-        <v>78845</v>
+        <v>57898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6687,34 +6674,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>439156</v>
+        <v>438971</v>
       </c>
       <c r="R63" t="n">
-        <v>6811687</v>
+        <v>6811657</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6747,6 +6742,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6773,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129649664</v>
+        <v>129649691</v>
       </c>
       <c r="B64" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6784,21 +6784,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>439138</v>
+        <v>439156</v>
       </c>
       <c r="R64" t="n">
-        <v>6811625</v>
+        <v>6811687</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129649687</v>
+        <v>129649696</v>
       </c>
       <c r="B65" t="n">
         <v>78845</v>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129649672</v>
+        <v>129649687</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6978,21 +6978,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438973</v>
+        <v>438968</v>
       </c>
       <c r="R66" t="n">
-        <v>6811633</v>
+        <v>6811757</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7067,7 +7067,7 @@
         <v>129649750</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129649696</v>
+        <v>129649672</v>
       </c>
       <c r="B68" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,21 +7172,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438968</v>
+        <v>438973</v>
       </c>
       <c r="R68" t="n">
-        <v>6811757</v>
+        <v>6811633</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7261,7 +7261,7 @@
         <v>129660884</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>129660888</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>129660834</v>
       </c>
       <c r="B71" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>129660891</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129660848</v>
+        <v>129660885</v>
       </c>
       <c r="B73" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7657,21 +7657,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7681,10 +7681,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438790</v>
+        <v>438717</v>
       </c>
       <c r="R73" t="n">
-        <v>6811814</v>
+        <v>6811848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129660885</v>
+        <v>129660856</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7754,21 +7754,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438717</v>
+        <v>438810</v>
       </c>
       <c r="R74" t="n">
-        <v>6811848</v>
+        <v>6811833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7840,10 +7840,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129660856</v>
+        <v>129660848</v>
       </c>
       <c r="B75" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438810</v>
+        <v>438790</v>
       </c>
       <c r="R75" t="n">
-        <v>6811833</v>
+        <v>6811814</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7940,7 +7940,7 @@
         <v>129660831</v>
       </c>
       <c r="B76" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>129660833</v>
       </c>
       <c r="B77" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>129660832</v>
       </c>
       <c r="B78" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8228,32 +8228,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129660839</v>
+        <v>129660841</v>
       </c>
       <c r="B79" t="n">
-        <v>57740</v>
+        <v>56930</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8261,7 +8261,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438773</v>
+        <v>438785</v>
       </c>
       <c r="R79" t="n">
-        <v>6811783</v>
+        <v>6811874</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129660855</v>
+        <v>129660839</v>
       </c>
       <c r="B80" t="n">
-        <v>78844</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8344,34 +8344,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438795</v>
+        <v>438773</v>
       </c>
       <c r="R80" t="n">
-        <v>6811815</v>
+        <v>6811783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8430,53 +8438,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129660841</v>
+        <v>129660855</v>
       </c>
       <c r="B81" t="n">
-        <v>56930</v>
+        <v>78845</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438785</v>
+        <v>438795</v>
       </c>
       <c r="R81" t="n">
-        <v>6811874</v>
+        <v>6811815</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8538,7 +8538,7 @@
         <v>129660835</v>
       </c>
       <c r="B82" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>129660886</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>129660890</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9036,10 +9036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129660844</v>
+        <v>129660836</v>
       </c>
       <c r="B87" t="n">
-        <v>91626</v>
+        <v>79678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9047,41 +9047,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438831</v>
+        <v>438795</v>
       </c>
       <c r="R87" t="n">
-        <v>6811826</v>
+        <v>6811868</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9122,7 +9115,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9141,10 +9133,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129660836</v>
+        <v>129660844</v>
       </c>
       <c r="B88" t="n">
-        <v>79677</v>
+        <v>91627</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9152,34 +9144,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Navardalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438795</v>
+        <v>438831</v>
       </c>
       <c r="R88" t="n">
-        <v>6811868</v>
+        <v>6811826</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9220,6 +9219,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47008-2025 artfynd.xlsx
+++ b/artfynd/A 47008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649677</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649725</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649726</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649727</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649728</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649729</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649730</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1761,6 +1816,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649731</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649732</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1955,6 +2020,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649733</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649734</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2149,6 +2224,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649735</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649736</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2440,6 +2530,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649738</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649739</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2634,6 +2734,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649740</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2731,6 +2836,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649741</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649742</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2925,6 +3040,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649743</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649744</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3119,6 +3244,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649745</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3216,6 +3346,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649746</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3313,6 +3448,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649747</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3410,6 +3550,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649748</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3507,6 +3652,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649749</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3604,6 +3754,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649750</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3701,6 +3856,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649751</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3798,6 +3958,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649752</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3895,6 +4060,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649753</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3992,6 +4162,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649754</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4089,6 +4264,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649755</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4186,6 +4366,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649756</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4283,6 +4468,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660880</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4380,6 +4570,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660884</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4477,6 +4672,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660885</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4574,6 +4774,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660886</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4671,6 +4876,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660887</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4768,6 +4978,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660888</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4865,6 +5080,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660890</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4962,6 +5182,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660891</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5059,6 +5284,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660892</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5156,6 +5386,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660893</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5253,6 +5488,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660894</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5350,6 +5590,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660895</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5447,6 +5692,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660896</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5544,6 +5794,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649696</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5641,6 +5896,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649697</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5738,6 +5998,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649698</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5835,6 +6100,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649699</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5932,6 +6202,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649700</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6029,6 +6304,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649701</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6126,6 +6406,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649702</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6223,6 +6508,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649703</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6320,6 +6610,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649704</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6417,6 +6712,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649705</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6514,6 +6814,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660855</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6611,6 +6916,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660856</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6708,6 +7018,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649660</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6805,6 +7120,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649661</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6902,6 +7222,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649662</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6999,6 +7324,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649663</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7096,6 +7426,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649664</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7193,6 +7528,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649665</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7290,6 +7630,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649666</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7387,6 +7732,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649667</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7484,6 +7834,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649668</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7581,6 +7936,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660831</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7678,6 +8038,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660832</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7775,6 +8140,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660833</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7880,6 +8250,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660845</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7982,6 +8357,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649670</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8079,6 +8459,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649671</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8176,6 +8561,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649672</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8281,6 +8671,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660839</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8386,6 +8781,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660840</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8491,6 +8891,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660841</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8596,6 +9001,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649679</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8701,6 +9111,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649680</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8811,6 +9226,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649681</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8916,6 +9336,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649682</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9021,6 +9446,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649683</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9126,6 +9556,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649684</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9231,6 +9666,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649685</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9333,6 +9773,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649675</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9443,6 +9888,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649676</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9548,6 +9998,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660842</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9645,6 +10100,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649687</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9742,6 +10202,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649688</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9839,6 +10304,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649689</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9936,6 +10406,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649690</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10033,6 +10508,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649691</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10130,6 +10610,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649692</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10227,6 +10712,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649693</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10324,6 +10814,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649694</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10421,6 +10916,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660848</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10518,6 +11018,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129649669</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10615,6 +11120,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660834</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10712,6 +11222,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660835</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10809,8 +11324,118 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>